--- a/mobility-theme/mobility-theme.xlsx
+++ b/mobility-theme/mobility-theme.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scrocca\Desktop\cefriel-github\controlled-vocabularies\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C2CFCE-BC47-4C00-8CB6-08DDEBD49C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B6A31C-5EDA-47E2-8551-22E6838A6B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,10 @@
     <sheet name="Delegated Regulations" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Vocabulary!$A$19:$I$195</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Vocabulary!$A$23:$I$200</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,7 +46,7 @@
     <author>tc={19405A8C-0548-4A9E-8E9A-505E9750B76D}</author>
   </authors>
   <commentList>
-    <comment ref="B193" authorId="0" shapeId="0" xr:uid="{19405A8C-0548-4A9E-8E9A-505E9750B76D}">
+    <comment ref="B197" authorId="0" shapeId="0" xr:uid="{19405A8C-0548-4A9E-8E9A-505E9750B76D}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="266">
   <si>
     <t>ConceptScheme URI</t>
   </si>
@@ -844,6 +845,18 @@
   </si>
   <si>
     <t>Mobility Theme</t>
+  </si>
+  <si>
+    <t>Darko Ilić (ASTRA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sara Guerra de Oliveira (University of Maribor) </t>
+  </si>
+  <si>
+    <t>Ed Ooms (NDW)</t>
+  </si>
+  <si>
+    <t>Christian Rantzow von Huth (Vejdirektoratet)</t>
   </si>
 </sst>
 </file>
@@ -1359,7 +1372,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="B193" dT="2026-05-18T09:16:59.14" personId="{FD7BA37A-6BBE-44AD-99FA-2A89ADEC35FA}" id="{19405A8C-0548-4A9E-8E9A-505E9750B76D}">
+  <threadedComment ref="B197" dT="2026-05-18T09:16:59.14" personId="{FD7BA37A-6BBE-44AD-99FA-2A89ADEC35FA}" id="{19405A8C-0548-4A9E-8E9A-505E9750B76D}">
     <text>duplicated under Public Transport category, missing DR information. Should we move it somewhere else?</text>
   </threadedComment>
 </ThreadedComments>
@@ -1367,7 +1380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I196"/>
+  <dimension ref="A1:I200"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="98.42578125" bestFit="1" customWidth="1"/>
@@ -1433,7 +1446,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
@@ -1465,296 +1478,236 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="14"/>
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" t="str">
-        <f>_xlfn.CONCAT(B1,"/",B11)</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/2.0.0</v>
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="6"/>
+        <v>9</v>
+      </c>
+      <c r="B14" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="14"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="str">
+        <f>_xlfn.CONCAT(B1,"/",B15)</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/2.0.0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="6"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B19" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B23" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="I23" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="str">
-        <f t="shared" ref="A20:A61" si="0">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B20,"/","-"))," ","-"),",",""))</f>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="str">
+        <f t="shared" ref="A24:A65" si="0">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B24,"/","-"))," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B24" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="11"/>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26" t="str">
-        <f>A20</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
-      </c>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" spans="1:9" ht="120" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/static-road-network-data</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="8"/>
-      <c r="E22" s="25" t="str">
-        <f>_xlfn.TEXTJOIN(", ",,A23:A32)</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/geometry, https://w3id.org/mobilitydcat-ap/mobility-theme/road-network-geometry, https://w3id.org/mobilitydcat-ap/mobility-theme/road-width, https://w3id.org/mobilitydcat-ap/mobility-theme/number-of-lanes, https://w3id.org/mobilitydcat-ap/mobility-theme/road-number-of-lanes, https://w3id.org/mobilitydcat-ap/mobility-theme/gradients, https://w3id.org/mobilitydcat-ap/mobility-theme/road-gradients, https://w3id.org/mobilitydcat-ap/mobility-theme/junctions, https://w3id.org/mobilitydcat-ap/mobility-theme/road-junctions, https://w3id.org/mobilitydcat-ap/mobility-theme/road-classification</v>
-      </c>
-      <c r="F22" s="1" t="str">
-        <f>A20</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
-      </c>
-      <c r="I22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/geometry</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="19"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G23" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" s="18" t="str">
-        <f>A24</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-network-geometry</v>
-      </c>
-      <c r="I23" s="17" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-network-geometry</v>
-      </c>
-      <c r="B24" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22" t="s">
-        <v>34</v>
-      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="11"/>
+      <c r="I24" s="1"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="str">
         <f t="shared" si="0"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26" t="str">
+        <f>A24</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
+      </c>
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/static-road-network-data</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="E26" s="25" t="str">
+        <f>_xlfn.TEXTJOIN(", ",,A27:A36)</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/geometry, https://w3id.org/mobilitydcat-ap/mobility-theme/road-network-geometry, https://w3id.org/mobilitydcat-ap/mobility-theme/road-width, https://w3id.org/mobilitydcat-ap/mobility-theme/number-of-lanes, https://w3id.org/mobilitydcat-ap/mobility-theme/road-number-of-lanes, https://w3id.org/mobilitydcat-ap/mobility-theme/gradients, https://w3id.org/mobilitydcat-ap/mobility-theme/road-gradients, https://w3id.org/mobilitydcat-ap/mobility-theme/junctions, https://w3id.org/mobilitydcat-ap/mobility-theme/road-junctions, https://w3id.org/mobilitydcat-ap/mobility-theme/road-classification</v>
+      </c>
+      <c r="F26" s="1" t="str">
+        <f>A24</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
+      </c>
+      <c r="I26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/geometry</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G27" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="18" t="str">
+        <f>A28</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-network-geometry</v>
+      </c>
+      <c r="I27" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-network-geometry</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="21"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="str">
+        <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-width</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B29" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="F25" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/number-of-lanes</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G26" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H26" s="18" t="str">
-        <f>A27</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-number-of-lanes</v>
-      </c>
-      <c r="I26" s="17" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-number-of-lanes</v>
-      </c>
-      <c r="B27" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="21"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/gradients</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G28" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="18" t="str">
-        <f>A29</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-gradients</v>
-      </c>
-      <c r="I28" s="17" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-gradients</v>
-      </c>
-      <c r="B29" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C29" s="21"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22" t="s">
+      <c r="C29" s="7"/>
+      <c r="F29" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I29" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/junctions</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/number-of-lanes</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C30" s="19"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
       <c r="F30" s="17" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="G30" s="18" t="b">
@@ -1762,7 +1715,7 @@
       </c>
       <c r="H30" s="18" t="str">
         <f>A31</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-junctions</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-number-of-lanes</v>
       </c>
       <c r="I30" s="17" t="s">
         <v>34</v>
@@ -1771,16 +1724,16 @@
     <row r="31" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="20" t="str">
         <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-junctions</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-number-of-lanes</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C31" s="21"/>
       <c r="D31" s="22"/>
       <c r="E31" s="22"/>
       <c r="F31" s="22" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="H31" s="22"/>
@@ -1788,332 +1741,360 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="10" t="str">
+    <row r="32" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-classification</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C32" s="7"/>
-      <c r="F32" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="105" x14ac:dyDescent="0.25">
-      <c r="A33" s="10" t="str">
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/gradients</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="19"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G32" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="18" t="str">
+        <f>A33</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-gradients</v>
+      </c>
+      <c r="I32" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="str">
         <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/cycle-network-data</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C33" s="8"/>
-      <c r="E33" s="25" t="str">
-        <f>_xlfn.TEXTJOIN(", ",,A34:A39)</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/network-geometry-and-lane-character, https://w3id.org/mobilitydcat-ap/mobility-theme/cycle-network-geometry, https://w3id.org/mobilitydcat-ap/mobility-theme/network-detailed-attributes, https://w3id.org/mobilitydcat-ap/mobility-theme/cycle-network-detailed-attributes, https://w3id.org/mobilitydcat-ap/mobility-theme/network-closures-diversions, https://w3id.org/mobilitydcat-ap/mobility-theme/cycle-network-closures-diversions</v>
-      </c>
-      <c r="F33" s="1" t="str">
-        <f>A20</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>46</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-gradients</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="21"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/network-geometry-and-lane-character</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C34" s="16"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/junctions</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="19"/>
       <c r="D34" s="17"/>
       <c r="E34" s="17"/>
       <c r="F34" s="17" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="G34" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="H34" s="17" t="s">
-        <v>48</v>
+      <c r="H34" s="18" t="str">
+        <f>A35</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-junctions</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="20" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B35,"/","-"))," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/cycle-network-geometry</v>
-      </c>
-      <c r="B35" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="C35" s="24"/>
-      <c r="D35" s="22" t="s">
-        <v>50</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-junctions</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="21"/>
+      <c r="D35" s="22"/>
       <c r="E35" s="22"/>
       <c r="F35" s="22" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="H35" s="22"/>
       <c r="I35" s="22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="str">
-        <f t="shared" ref="A36" si="1">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B36,"/","-"))," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/network-detailed-attributes</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C36" s="16"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G36" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H36" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="I36" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="20" t="str">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/cycle-network-detailed-attributes</v>
-      </c>
-      <c r="B37" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" s="24"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H37" s="22"/>
-      <c r="I37" s="22" t="s">
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-classification</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="F36" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/cycle-network-data</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="8"/>
+      <c r="E37" s="25" t="str">
+        <f>_xlfn.TEXTJOIN(", ",,A38:A43)</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/network-geometry-and-lane-character, https://w3id.org/mobilitydcat-ap/mobility-theme/cycle-network-geometry, https://w3id.org/mobilitydcat-ap/mobility-theme/network-detailed-attributes, https://w3id.org/mobilitydcat-ap/mobility-theme/cycle-network-detailed-attributes, https://w3id.org/mobilitydcat-ap/mobility-theme/network-closures-diversions, https://w3id.org/mobilitydcat-ap/mobility-theme/cycle-network-closures-diversions</v>
+      </c>
+      <c r="F37" s="1" t="str">
+        <f>A24</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B38,"/","-"))," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/network-closures-diversions</v>
+        <f t="shared" si="0"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/network-geometry-and-lane-character</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C38" s="16"/>
       <c r="D38" s="17"/>
       <c r="E38" s="17"/>
       <c r="F38" s="17" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="G38" s="18" t="b">
         <v>1</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="I38" s="17"/>
+        <v>48</v>
+      </c>
+      <c r="I38" s="17" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="39" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="20" t="str">
         <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B39,"/","-"))," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/cycle-network-closures-diversions</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/cycle-network-geometry</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C39" s="24"/>
-      <c r="D39" s="22"/>
+      <c r="D39" s="22" t="s">
+        <v>50</v>
+      </c>
       <c r="E39" s="22"/>
       <c r="F39" s="22" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="H39" s="22"/>
-      <c r="I39" s="22"/>
-    </row>
-    <row r="40" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A40" s="10" t="str">
+      <c r="I39" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="15" t="str">
+        <f t="shared" ref="A40" si="1">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B40,"/","-"))," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/network-detailed-attributes</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" s="16"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G40" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="I40" s="18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/cycle-network-detailed-attributes</v>
+      </c>
+      <c r="B41" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="24"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="15" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B42,"/","-"))," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/network-closures-diversions</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" s="16"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G42" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H42" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="I42" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="20" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B43,"/","-"))," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/cycle-network-closures-diversions</v>
+      </c>
+      <c r="B43" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" s="24"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H43" s="22"/>
+      <c r="I43" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="10" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/pedestrian-network-data</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B44" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C40" s="8"/>
-      <c r="E40" s="1" t="str">
-        <f>CONCATENATE(A41,", ",A42)</f>
+      <c r="C44" s="8"/>
+      <c r="E44" s="1" t="str">
+        <f>CONCATENATE(A45,", ",A46)</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/pedestrian-network-geometry, https://w3id.org/mobilitydcat-ap/mobility-theme/pedestrian-accessibility-facilities</v>
       </c>
-      <c r="F40" s="1" t="str">
-        <f>A20</f>
+      <c r="F44" s="1" t="str">
+        <f>A24</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/pedestrian-network-geometry</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C41" s="8"/>
-      <c r="F41" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/pedestrian-accessibility-facilities</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C42" s="8"/>
-      <c r="F42" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/static-traffic-signs-and-regulations</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C43" s="8"/>
-      <c r="E43" s="25" t="str">
-        <f>_xlfn.TEXTJOIN(", ",,A44:A54)</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/tunnel-access-conditions, https://w3id.org/mobilitydcat-ap/mobility-theme/bridge-access-conditions, https://w3id.org/mobilitydcat-ap/mobility-theme/speed-limits, https://w3id.org/mobilitydcat-ap/mobility-theme/other-static-traffic-signs, https://w3id.org/mobilitydcat-ap/mobility-theme/permanent-access-restrictions, https://w3id.org/mobilitydcat-ap/mobility-theme/other-traffic-regulations, https://w3id.org/mobilitydcat-ap/mobility-theme/traffic-circulation-plans, https://w3id.org/mobilitydcat-ap/mobility-theme/static-overtaking-bans-on-heavy-goods-vehicles, https://w3id.org/mobilitydcat-ap/mobility-theme/weight-length-width-height-restrictions, https://w3id.org/mobilitydcat-ap/mobility-theme/one-way-streets, https://w3id.org/mobilitydcat-ap/mobility-theme/regulated-traffic-zones</v>
-      </c>
-      <c r="F43" s="1" t="str">
-        <f>A20</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/tunnel-access-conditions</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C44" s="8"/>
-      <c r="F44" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
       <c r="I44" s="1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bridge-access-conditions</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>62</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/pedestrian-network-geometry</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="C45" s="8"/>
       <c r="F45" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/speed-limits</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>63</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/pedestrian-accessibility-facilities</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>59</v>
       </c>
       <c r="C46" s="8"/>
       <c r="F46" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/other-static-traffic-signs</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>64</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/static-traffic-signs-and-regulations</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>60</v>
       </c>
       <c r="C47" s="8"/>
+      <c r="E47" s="25" t="str">
+        <f>_xlfn.TEXTJOIN(", ",,A48:A58)</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/tunnel-access-conditions, https://w3id.org/mobilitydcat-ap/mobility-theme/bridge-access-conditions, https://w3id.org/mobilitydcat-ap/mobility-theme/speed-limits, https://w3id.org/mobilitydcat-ap/mobility-theme/other-static-traffic-signs, https://w3id.org/mobilitydcat-ap/mobility-theme/permanent-access-restrictions, https://w3id.org/mobilitydcat-ap/mobility-theme/other-traffic-regulations, https://w3id.org/mobilitydcat-ap/mobility-theme/traffic-circulation-plans, https://w3id.org/mobilitydcat-ap/mobility-theme/static-overtaking-bans-on-heavy-goods-vehicles, https://w3id.org/mobilitydcat-ap/mobility-theme/weight-length-width-height-restrictions, https://w3id.org/mobilitydcat-ap/mobility-theme/one-way-streets, https://w3id.org/mobilitydcat-ap/mobility-theme/regulated-traffic-zones</v>
+      </c>
       <c r="F47" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I47" s="25" t="s">
+        <f>A24</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
+      </c>
+      <c r="I47" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/permanent-access-restrictions</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/tunnel-access-conditions</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C48" s="8"/>
       <c r="F48" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I48" s="1" t="s">
@@ -2123,14 +2104,14 @@
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/other-traffic-regulations</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bridge-access-conditions</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C49" s="8"/>
       <c r="F49" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I49" s="1" t="s">
@@ -2140,907 +2121,921 @@
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/traffic-circulation-plans</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/speed-limits</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C50" s="8"/>
       <c r="F50" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="51" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="20" t="str">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/other-static-traffic-signs</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C51" s="8"/>
+      <c r="F51" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I51" s="25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/permanent-access-restrictions</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C52" s="8"/>
+      <c r="F52" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/other-traffic-regulations</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C53" s="8"/>
+      <c r="F53" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/traffic-circulation-plans</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C54" s="8"/>
+      <c r="F54" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="20" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/static-overtaking-bans-on-heavy-goods-vehicles</v>
       </c>
-      <c r="B51" s="24" t="s">
+      <c r="B55" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="C51" s="8"/>
-      <c r="D51" s="22"/>
-      <c r="E51" s="22"/>
-      <c r="F51" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H51" s="22"/>
-      <c r="I51" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="20" t="str">
+      <c r="C55" s="8"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H55" s="22"/>
+      <c r="I55" s="22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="20" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/weight-length-width-height-restrictions</v>
       </c>
-      <c r="B52" s="24" t="s">
+      <c r="B56" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="C52" s="8"/>
-      <c r="D52" s="22"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H52" s="22"/>
-      <c r="I52" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="20" t="str">
+      <c r="C56" s="8"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H56" s="22"/>
+      <c r="I56" s="22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="20" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/one-way-streets</v>
       </c>
-      <c r="B53" s="24" t="s">
+      <c r="B57" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="C53" s="8"/>
-      <c r="D53" s="22"/>
-      <c r="E53" s="22"/>
-      <c r="F53" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H53" s="22"/>
-      <c r="I53" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" s="23" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A54" s="20" t="str">
+      <c r="C57" s="8"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H57" s="22"/>
+      <c r="I57" s="22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" s="23" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A58" s="20" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/regulated-traffic-zones</v>
       </c>
-      <c r="B54" s="24" t="s">
+      <c r="B58" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="C54" s="8"/>
-      <c r="D54" s="22" t="s">
+      <c r="C58" s="8"/>
+      <c r="D58" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H54" s="22"/>
-      <c r="I54" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="105" x14ac:dyDescent="0.25">
-      <c r="A55" s="10" t="str">
+      <c r="E58" s="22"/>
+      <c r="F58" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H58" s="22"/>
+      <c r="I58" s="22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A59" s="10" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/toll-information</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B59" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C55" s="8"/>
-      <c r="E55" s="25" t="str">
-        <f>_xlfn.TEXTJOIN(", ",,A56:A61)</f>
+      <c r="C59" s="8"/>
+      <c r="E59" s="25" t="str">
+        <f>_xlfn.TEXTJOIN(", ",,A60:A65)</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-of-tolling-stations, https://w3id.org/mobilitydcat-ap/mobility-theme/identification-of-tolled-roads, https://w3id.org/mobilitydcat-ap/mobility-theme/applicable-road-user-charges-and-payment-methods, https://w3id.org/mobilitydcat-ap/mobility-theme/fixed-road-user-charges-and-payment-methods, https://w3id.org/mobilitydcat-ap/mobility-theme/variable-road-user-charges-and-payment-methods, https://w3id.org/mobilitydcat-ap/mobility-theme/payment-methods-for-tolls</v>
       </c>
-      <c r="F55" s="1" t="str">
-        <f>A20</f>
+      <c r="F59" s="1" t="str">
+        <f>A24</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
-      <c r="I55" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="10" t="str">
+      <c r="I59" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="10" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-of-tolling-stations</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B60" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C56" s="8"/>
-      <c r="F56" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="10" t="str">
+      <c r="C60" s="8"/>
+      <c r="F60" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="10" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/identification-of-tolled-roads</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B61" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C57" s="8"/>
-      <c r="F57" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" s="18" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="15" t="str">
+      <c r="C61" s="8"/>
+      <c r="F61" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" s="18" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="15" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/applicable-road-user-charges-and-payment-methods</v>
       </c>
-      <c r="B58" s="16" t="s">
+      <c r="B62" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C58" s="16"/>
-      <c r="D58" s="17"/>
-      <c r="E58" s="17"/>
-      <c r="F58" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G58" s="18" t="b">
+      <c r="C62" s="16"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G62" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="H58" s="17" t="str">
-        <f>A59</f>
+      <c r="H62" s="17" t="str">
+        <f>A63</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/fixed-road-user-charges-and-payment-methods</v>
       </c>
-      <c r="I58" s="18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="20" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B59,"/","-"))," ","-"),",",""))</f>
+      <c r="I62" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="20" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B63,"/","-"))," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/fixed-road-user-charges-and-payment-methods</v>
       </c>
-      <c r="B59" s="24" t="s">
+      <c r="B63" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="C59" s="24"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H59" s="22"/>
-      <c r="I59" s="23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="20" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B60,"/","-"))," ","-"),",",""))</f>
+      <c r="C63" s="24"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H63" s="22"/>
+      <c r="I63" s="23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="20" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B64,"/","-"))," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/variable-road-user-charges-and-payment-methods</v>
       </c>
-      <c r="B60" s="24" t="s">
+      <c r="B64" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="C60" s="24"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="22"/>
-      <c r="F60" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H60" s="22"/>
-      <c r="I60" s="23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" s="18" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="15" t="str">
+      <c r="C64" s="24"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H64" s="22"/>
+      <c r="I64" s="23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" s="18" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="15" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/payment-methods-for-tolls</v>
       </c>
-      <c r="B61" s="16" t="s">
+      <c r="B65" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C61" s="16"/>
-      <c r="D61" s="17"/>
-      <c r="E61" s="17"/>
-      <c r="F61" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G61" s="18" t="b">
+      <c r="C65" s="16"/>
+      <c r="D65" s="17"/>
+      <c r="E65" s="17"/>
+      <c r="F65" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G65" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="H61" s="17" t="str">
-        <f>_xlfn.CONCAT(A59,",",A60)</f>
+      <c r="H65" s="17" t="str">
+        <f>_xlfn.CONCAT(A63,",",A64)</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/fixed-road-user-charges-and-payment-methods,https://w3id.org/mobilitydcat-ap/mobility-theme/variable-road-user-charges-and-payment-methods</v>
       </c>
-      <c r="I61" s="17" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="144" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="10" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B62,"/","-"))," ","-"),",",""))</f>
+      <c r="I65" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="10" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B66,"/","-"))," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-service-and-rest-area-information</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B66" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C62" s="8"/>
-      <c r="E62" s="25" t="str">
-        <f>_xlfn.TEXTJOIN(", ",,A63:A79)</f>
+      <c r="C66" s="8"/>
+      <c r="E66" s="25" t="str">
+        <f>_xlfn.TEXTJOIN(", ",,A67:A83)</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/car-parking-locations-and-conditions, https://w3id.org/mobilitydcat-ap/mobility-theme/car-parking-availability, https://w3id.org/mobilitydcat-ap/mobility-theme/parking-locations-description-and-facilities, https://w3id.org/mobilitydcat-ap/mobility-theme/parking-zones, https://w3id.org/mobilitydcat-ap/mobility-theme/parking-real-time-availability, https://w3id.org/mobilitydcat-ap/mobility-theme/parking-conditions-and-tariffs, https://w3id.org/mobilitydcat-ap/mobility-theme/parking-payment-points-and-methods, https://w3id.org/mobilitydcat-ap/mobility-theme/service-and-rest-area-locations-and-conditions, https://w3id.org/mobilitydcat-ap/mobility-theme/service-and-rest-area-locations-description-and-facilities, https://w3id.org/mobilitydcat-ap/mobility-theme/service-and-rest-area-availability, https://w3id.org/mobilitydcat-ap/mobility-theme/service-and-rest-area-real-time-availability, https://w3id.org/mobilitydcat-ap/mobility-theme/truck-parking-locations-and-conditions, https://w3id.org/mobilitydcat-ap/mobility-theme/truck-parking-availability, https://w3id.org/mobilitydcat-ap/mobility-theme/park-and-ride-stops, https://w3id.org/mobilitydcat-ap/mobility-theme/park-and-drive-stops, https://w3id.org/mobilitydcat-ap/mobility-theme/kiss-and-ride-stops, https://w3id.org/mobilitydcat-ap/mobility-theme/bike-parking-locations</v>
       </c>
-      <c r="F62" s="1" t="str">
-        <f>A20</f>
+      <c r="F66" s="1" t="str">
+        <f>A24</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
-      <c r="I62" s="1" t="s">
+      <c r="I66" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="63" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A63" s="15" t="str">
-        <f t="shared" ref="A63:A150" si="2">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B63,"/","-"))," ","-"),",",""))</f>
+    <row r="67" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="15" t="str">
+        <f t="shared" ref="A67:A154" si="2">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B67,"/","-"))," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/car-parking-locations-and-conditions</v>
       </c>
-      <c r="B63" s="16" t="s">
+      <c r="B67" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C63" s="16"/>
-      <c r="D63" s="17"/>
-      <c r="E63" s="17"/>
-      <c r="F63" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G63" s="18" t="b">
+      <c r="C67" s="16"/>
+      <c r="D67" s="17"/>
+      <c r="E67" s="17"/>
+      <c r="F67" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G67" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="H63" s="17" t="str">
-        <f>A65</f>
+      <c r="H67" s="17" t="str">
+        <f>A69</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-locations-description-and-facilities</v>
       </c>
-      <c r="I63" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A64" s="15" t="str">
+      <c r="I67" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="15" t="str">
         <f t="shared" si="2"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/car-parking-availability</v>
       </c>
-      <c r="B64" s="16" t="s">
+      <c r="B68" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C64" s="16"/>
-      <c r="D64" s="17"/>
-      <c r="E64" s="17"/>
-      <c r="F64" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G64" s="18" t="b">
+      <c r="C68" s="16"/>
+      <c r="D68" s="17"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G68" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="H64" s="17" t="str">
-        <f>A67</f>
+      <c r="H68" s="17" t="str">
+        <f>A71</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-real-time-availability</v>
       </c>
-      <c r="I64" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="20" t="str">
+      <c r="I68" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="20" t="str">
         <f t="shared" si="2"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-locations-description-and-facilities</v>
       </c>
-      <c r="B65" s="24" t="s">
+      <c r="B69" s="24" t="s">
         <v>84</v>
       </c>
-      <c r="C65" s="24"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H65" s="22"/>
-      <c r="I65" s="22"/>
-    </row>
-    <row r="66" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-zones</v>
-      </c>
-      <c r="B66" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="C66" s="24"/>
-      <c r="D66" s="22"/>
-      <c r="E66" s="22"/>
-      <c r="F66" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H66" s="22"/>
-      <c r="I66" s="22"/>
-    </row>
-    <row r="67" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-real-time-availability</v>
-      </c>
-      <c r="B67" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C67" s="24"/>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H67" s="22"/>
-      <c r="I67" s="22"/>
-    </row>
-    <row r="68" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-conditions-and-tariffs</v>
-      </c>
-      <c r="B68" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="C68" s="24"/>
-      <c r="D68" s="22"/>
-      <c r="E68" s="22"/>
-      <c r="F68" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H68" s="22"/>
-      <c r="I68" s="22"/>
-    </row>
-    <row r="69" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A69" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-payment-points-and-methods</v>
-      </c>
-      <c r="B69" s="24" t="s">
-        <v>88</v>
-      </c>
       <c r="C69" s="24"/>
-      <c r="D69" s="22" t="s">
-        <v>89</v>
-      </c>
+      <c r="D69" s="22"/>
       <c r="E69" s="22"/>
       <c r="F69" s="22" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="H69" s="22"/>
-      <c r="I69" s="22"/>
-    </row>
-    <row r="70" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A70" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-and-rest-area-locations-and-conditions</v>
-      </c>
-      <c r="B70" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C70" s="16"/>
-      <c r="D70" s="17"/>
-      <c r="E70" s="17"/>
-      <c r="F70" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G70" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H70" s="17" t="str">
-        <f>A71</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-and-rest-area-locations-description-and-facilities</v>
-      </c>
-      <c r="I70" s="17" t="s">
-        <v>34</v>
+      <c r="I69" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-zones</v>
+      </c>
+      <c r="B70" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="C70" s="24"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H70" s="22"/>
+      <c r="I70" s="22" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="71" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-and-rest-area-locations-description-and-facilities</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-real-time-availability</v>
       </c>
       <c r="B71" s="24" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C71" s="24"/>
       <c r="D71" s="22"/>
       <c r="E71" s="22"/>
       <c r="F71" s="22" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="H71" s="22"/>
-      <c r="I71" s="22"/>
-    </row>
-    <row r="72" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A72" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-and-rest-area-availability</v>
-      </c>
-      <c r="B72" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="C72" s="16"/>
-      <c r="D72" s="17"/>
-      <c r="E72" s="17"/>
-      <c r="F72" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G72" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H72" s="17" t="str">
-        <f>A73</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-and-rest-area-real-time-availability</v>
-      </c>
-      <c r="I72" s="17"/>
-    </row>
-    <row r="73" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I71" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-conditions-and-tariffs</v>
+      </c>
+      <c r="B72" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="C72" s="24"/>
+      <c r="D72" s="22"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H72" s="22"/>
+      <c r="I72" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-and-rest-area-real-time-availability</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-payment-points-and-methods</v>
       </c>
       <c r="B73" s="24" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C73" s="24"/>
-      <c r="D73" s="22"/>
+      <c r="D73" s="22" t="s">
+        <v>89</v>
+      </c>
       <c r="E73" s="22"/>
       <c r="F73" s="22" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="H73" s="22"/>
-      <c r="I73" s="22"/>
+      <c r="I73" s="22" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="74" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/truck-parking-locations-and-conditions</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-and-rest-area-locations-and-conditions</v>
       </c>
       <c r="B74" s="16" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C74" s="16"/>
       <c r="D74" s="17"/>
       <c r="E74" s="17"/>
       <c r="F74" s="17" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="G74" s="18" t="b">
         <v>1</v>
       </c>
       <c r="H74" s="17" t="str">
-        <f>A65</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-locations-description-and-facilities</v>
+        <f>A75</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-and-rest-area-locations-description-and-facilities</v>
       </c>
       <c r="I74" s="17" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A75" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/truck-parking-availability</v>
-      </c>
-      <c r="B75" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C75" s="16"/>
-      <c r="D75" s="17"/>
-      <c r="E75" s="17"/>
-      <c r="F75" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G75" s="18" t="b">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-and-rest-area-locations-description-and-facilities</v>
+      </c>
+      <c r="B75" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C75" s="24"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H75" s="22"/>
+      <c r="I75" s="23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-and-rest-area-availability</v>
+      </c>
+      <c r="B76" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C76" s="16"/>
+      <c r="D76" s="17"/>
+      <c r="E76" s="17"/>
+      <c r="F76" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G76" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="H75" s="17" t="str">
-        <f>A67</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-real-time-availability</v>
-      </c>
-      <c r="I75" s="17" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A76" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/park-and-ride-stops</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="C76" s="8"/>
-      <c r="D76" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F76" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="H76" s="17" t="str">
+        <f>A77</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-and-rest-area-real-time-availability</v>
+      </c>
+      <c r="I76" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/park-and-drive-stops</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-and-rest-area-real-time-availability</v>
       </c>
       <c r="B77" s="24" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C77" s="24"/>
-      <c r="D77" s="22" t="s">
-        <v>100</v>
-      </c>
+      <c r="D77" s="22"/>
       <c r="E77" s="22"/>
       <c r="F77" s="22" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="H77" s="22"/>
-      <c r="I77" s="22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/kiss-and-ride-stops</v>
-      </c>
-      <c r="B78" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="C78" s="24"/>
-      <c r="D78" s="22"/>
-      <c r="E78" s="22"/>
-      <c r="F78" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H78" s="22"/>
-      <c r="I78" s="22"/>
-    </row>
-    <row r="79" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="I77" s="23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/truck-parking-locations-and-conditions</v>
+      </c>
+      <c r="B78" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C78" s="16"/>
+      <c r="D78" s="17"/>
+      <c r="E78" s="17"/>
+      <c r="F78" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G78" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H78" s="17" t="str">
+        <f>A69</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-locations-description-and-facilities</v>
+      </c>
+      <c r="I78" s="17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="15" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bike-parking-locations</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/truck-parking-availability</v>
       </c>
       <c r="B79" s="16" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C79" s="16"/>
       <c r="D79" s="17"/>
       <c r="E79" s="17"/>
       <c r="F79" s="17" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="G79" s="18" t="b">
         <v>1</v>
       </c>
       <c r="H79" s="17" t="str">
-        <f>A65</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-locations-description-and-facilities</v>
+        <f>A71</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-real-time-availability</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/filling-and-charging-stations</v>
-      </c>
-      <c r="B80" s="9" t="s">
-        <v>103</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/park-and-ride-stops</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>97</v>
       </c>
       <c r="C80" s="8"/>
-      <c r="E80" s="25" t="str">
-        <f>_xlfn.TEXTJOIN(", ",,A85:A87)</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-characteristics-filling-charging-stations, https://w3id.org/mobilitydcat-ap/mobility-theme/availability-filling-charging-stations, https://w3id.org/mobilitydcat-ap/mobility-theme/prices-of-filling-charging-stations</v>
+      <c r="D80" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="F80" s="1" t="str">
-        <f>A20</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
-      </c>
-      <c r="I80" s="25" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A81" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-conditions-of-charging-points</v>
-      </c>
-      <c r="B81" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="C81" s="16"/>
-      <c r="D81" s="17"/>
-      <c r="E81" s="17"/>
-      <c r="F81" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G81" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H81" s="17" t="str">
-        <f>A85</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-characteristics-filling-charging-stations</v>
-      </c>
-      <c r="I81" s="17" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A82" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-conditions-of-filling-stations</v>
-      </c>
-      <c r="B82" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="17"/>
-      <c r="E82" s="17"/>
-      <c r="F82" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G82" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H82" s="17" t="str">
-        <f>A85</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-characteristics-filling-charging-stations</v>
-      </c>
-      <c r="I82" s="17" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/park-and-drive-stops</v>
+      </c>
+      <c r="B81" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C81" s="24"/>
+      <c r="D81" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="E81" s="22"/>
+      <c r="F81" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H81" s="22"/>
+      <c r="I81" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/kiss-and-ride-stops</v>
+      </c>
+      <c r="B82" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="C82" s="24"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="F82" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H82" s="22"/>
+      <c r="I82" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="15" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/availability-of-charging-points-for-electric-vehicles</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bike-parking-locations</v>
       </c>
       <c r="B83" s="16" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C83" s="16"/>
       <c r="D83" s="17"/>
       <c r="E83" s="17"/>
       <c r="F83" s="17" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="G83" s="18" t="b">
         <v>1</v>
       </c>
       <c r="H83" s="17" t="str">
-        <f>A86</f>
+        <f>A69</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-locations-description-and-facilities</v>
+      </c>
+      <c r="I83" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A84" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/filling-and-charging-stations</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C84" s="8"/>
+      <c r="E84" s="25" t="str">
+        <f>_xlfn.TEXTJOIN(", ",,A89:A91)</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-characteristics-filling-charging-stations, https://w3id.org/mobilitydcat-ap/mobility-theme/availability-filling-charging-stations, https://w3id.org/mobilitydcat-ap/mobility-theme/prices-of-filling-charging-stations</v>
+      </c>
+      <c r="F84" s="1" t="str">
+        <f>A24</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
+      </c>
+      <c r="I84" s="25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A85" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-conditions-of-charging-points</v>
+      </c>
+      <c r="B85" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C85" s="16"/>
+      <c r="D85" s="17"/>
+      <c r="E85" s="17"/>
+      <c r="F85" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G85" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H85" s="17" t="str">
+        <f>A89</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-characteristics-filling-charging-stations</v>
+      </c>
+      <c r="I85" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A86" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-conditions-of-filling-stations</v>
+      </c>
+      <c r="B86" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="C86" s="16"/>
+      <c r="D86" s="17"/>
+      <c r="E86" s="17"/>
+      <c r="F86" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G86" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H86" s="17" t="str">
+        <f>A89</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-characteristics-filling-charging-stations</v>
+      </c>
+      <c r="I86" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A87" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/availability-of-charging-points-for-electric-vehicles</v>
+      </c>
+      <c r="B87" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="C87" s="16"/>
+      <c r="D87" s="17"/>
+      <c r="E87" s="17"/>
+      <c r="F87" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G87" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H87" s="17" t="str">
+        <f>A90</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/availability-filling-charging-stations</v>
       </c>
-      <c r="I83" s="17" t="s">
+      <c r="I87" s="17" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="84" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="15" t="str">
+    <row r="88" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="15" t="str">
         <f t="shared" si="2"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/availability-of-filling-stations</v>
       </c>
-      <c r="B84" s="16" t="s">
+      <c r="B88" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C84" s="16"/>
-      <c r="D84" s="17"/>
-      <c r="E84" s="17"/>
-      <c r="F84" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G84" s="18" t="b">
+      <c r="C88" s="16"/>
+      <c r="D88" s="17"/>
+      <c r="E88" s="17"/>
+      <c r="F88" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G88" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="H84" s="17" t="str">
-        <f>A86</f>
+      <c r="H88" s="17" t="str">
+        <f>A90</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/availability-filling-charging-stations</v>
       </c>
-      <c r="I84" s="17" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A85" s="20" t="s">
+      <c r="I88" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A89" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="B85" s="24" t="s">
+      <c r="B89" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="C85" s="24"/>
-      <c r="D85" s="22"/>
-      <c r="E85" s="22"/>
-      <c r="F85" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H85" s="22"/>
-      <c r="I85" s="22" t="s">
+      <c r="C89" s="24"/>
+      <c r="D89" s="22"/>
+      <c r="E89" s="22"/>
+      <c r="F89" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H89" s="22"/>
+      <c r="I89" s="22" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="86" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A86" s="20" t="s">
+    <row r="90" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A90" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="B86" s="24" t="s">
+      <c r="B90" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="C86" s="24"/>
-      <c r="D86" s="22"/>
-      <c r="E86" s="22"/>
-      <c r="F86" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H86" s="22"/>
-      <c r="I86" s="22" t="s">
+      <c r="C90" s="24"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="F90" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H90" s="22"/>
+      <c r="I90" s="22" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="87" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A87" s="20" t="s">
+    <row r="91" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A91" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="B87" s="24" t="s">
+      <c r="B91" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="C87" s="24"/>
-      <c r="D87" s="22"/>
-      <c r="E87" s="22"/>
-      <c r="F87" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H87" s="22"/>
-      <c r="I87" s="22" t="s">
+      <c r="C91" s="24"/>
+      <c r="D91" s="22"/>
+      <c r="E91" s="22"/>
+      <c r="F91" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H91" s="22"/>
+      <c r="I91" s="22" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A88" s="10" t="str">
+    <row r="92" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A92" s="10" t="str">
         <f t="shared" si="2"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/freight-and-logistics</v>
       </c>
-      <c r="B88" s="9" t="s">
+      <c r="B92" s="9" t="s">
         <v>115</v>
-      </c>
-      <c r="C88" s="8"/>
-      <c r="E88" s="1" t="str">
-        <f>CONCATENATE(A89,", ",A90,", ",A91)</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/freight-delivery-regulations, https://w3id.org/mobilitydcat-ap/mobility-theme/location-of-delivery-areas, https://w3id.org/mobilitydcat-ap/mobility-theme/availability-of-delivery-areas</v>
-      </c>
-      <c r="F88" s="1" t="str">
-        <f>A20</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
-      </c>
-      <c r="I88" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/freight-delivery-regulations</v>
-      </c>
-      <c r="B89" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C89" s="8"/>
-      <c r="F89" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I89" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-of-delivery-areas</v>
-      </c>
-      <c r="B90" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="C90" s="8"/>
-      <c r="F90" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/availability-of-delivery-areas</v>
-      </c>
-      <c r="B91" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="C91" s="8"/>
-      <c r="F91" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" ht="165" x14ac:dyDescent="0.25">
-      <c r="A92" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/dynamic-traffic-signs-and-regulations</v>
-      </c>
-      <c r="B92" s="9" t="s">
-        <v>119</v>
       </c>
       <c r="C92" s="8"/>
       <c r="E92" s="1" t="str">
-        <f>CONCATENATE(A93,", ",A94,", ",A95,", ",A96,", ",A97,", ",A98,", ",A99,", ",A100,", ",A101)</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-closures-and-access-conditions, https://w3id.org/mobilitydcat-ap/mobility-theme/lane-closures-and-access-conditions, https://w3id.org/mobilitydcat-ap/mobility-theme/bridge-closures-and-access-conditions, https://w3id.org/mobilitydcat-ap/mobility-theme/tunnel-closures-and-access-conditions, https://w3id.org/mobilitydcat-ap/mobility-theme/other-access-restrictions-and-traffic-regulations, https://w3id.org/mobilitydcat-ap/mobility-theme/dynamic-overtaking-bans-on-heavy-goods-vehicles, https://w3id.org/mobilitydcat-ap/mobility-theme/dynamic-speed-limits, https://w3id.org/mobilitydcat-ap/mobility-theme/direction-of-travel-on-reversible-lanes, https://w3id.org/mobilitydcat-ap/mobility-theme/other-temporary-traffic-management-measures-or-plans</v>
+        <f>CONCATENATE(A93,", ",A94,", ",A95)</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/freight-delivery-regulations, https://w3id.org/mobilitydcat-ap/mobility-theme/location-of-delivery-areas, https://w3id.org/mobilitydcat-ap/mobility-theme/availability-of-delivery-areas</v>
       </c>
       <c r="F92" s="1" t="str">
-        <f>A20</f>
+        <f>A24</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
       <c r="I92" s="1" t="s">
@@ -3050,14 +3045,14 @@
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-closures-and-access-conditions</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/freight-delivery-regulations</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C93" s="8"/>
       <c r="F93" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I93" s="1" t="s">
@@ -3067,14 +3062,14 @@
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/lane-closures-and-access-conditions</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-of-delivery-areas</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C94" s="8"/>
       <c r="F94" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I94" s="1" t="s">
@@ -3084,32 +3079,36 @@
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bridge-closures-and-access-conditions</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/availability-of-delivery-areas</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C95" s="8"/>
       <c r="F95" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A96" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/tunnel-closures-and-access-conditions</v>
-      </c>
-      <c r="B96" s="8" t="s">
-        <v>123</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/dynamic-traffic-signs-and-regulations</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>119</v>
       </c>
       <c r="C96" s="8"/>
+      <c r="E96" s="1" t="str">
+        <f>CONCATENATE(A97,", ",A98,", ",A99,", ",A100,", ",A101,", ",A102,", ",A103,", ",A104,", ",A105)</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-closures-and-access-conditions, https://w3id.org/mobilitydcat-ap/mobility-theme/lane-closures-and-access-conditions, https://w3id.org/mobilitydcat-ap/mobility-theme/bridge-closures-and-access-conditions, https://w3id.org/mobilitydcat-ap/mobility-theme/tunnel-closures-and-access-conditions, https://w3id.org/mobilitydcat-ap/mobility-theme/other-access-restrictions-and-traffic-regulations, https://w3id.org/mobilitydcat-ap/mobility-theme/dynamic-overtaking-bans-on-heavy-goods-vehicles, https://w3id.org/mobilitydcat-ap/mobility-theme/dynamic-speed-limits, https://w3id.org/mobilitydcat-ap/mobility-theme/direction-of-travel-on-reversible-lanes, https://w3id.org/mobilitydcat-ap/mobility-theme/other-temporary-traffic-management-measures-or-plans</v>
+      </c>
       <c r="F96" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+        <f>A24</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>34</v>
@@ -3118,14 +3117,14 @@
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/other-access-restrictions-and-traffic-regulations</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-closures-and-access-conditions</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C97" s="8"/>
       <c r="F97" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I97" s="1" t="s">
@@ -3135,14 +3134,14 @@
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/dynamic-overtaking-bans-on-heavy-goods-vehicles</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/lane-closures-and-access-conditions</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C98" s="8"/>
       <c r="F98" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I98" s="1" t="s">
@@ -3152,14 +3151,14 @@
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/dynamic-speed-limits</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bridge-closures-and-access-conditions</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C99" s="8"/>
       <c r="F99" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I99" s="1" t="s">
@@ -3169,14 +3168,14 @@
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/direction-of-travel-on-reversible-lanes</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/tunnel-closures-and-access-conditions</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C100" s="8"/>
       <c r="F100" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I100" s="1" t="s">
@@ -3186,352 +3185,328 @@
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/other-temporary-traffic-management-measures-or-plans</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/other-access-restrictions-and-traffic-regulations</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C101" s="8"/>
       <c r="F101" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-work-information</v>
-      </c>
-      <c r="B102" s="9" t="s">
-        <v>129</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/dynamic-overtaking-bans-on-heavy-goods-vehicles</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>125</v>
       </c>
       <c r="C102" s="8"/>
-      <c r="E102" s="1" t="str">
-        <f>CONCATENATE(A103,", ",A104)</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/long-term-road-works, https://w3id.org/mobilitydcat-ap/mobility-theme/short-term-road-works</v>
-      </c>
       <c r="F102" s="1" t="str">
-        <f>A20</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/long-term-road-works</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/dynamic-speed-limits</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C103" s="8"/>
       <c r="F103" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/short-term-road-works</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/direction-of-travel-on-reversible-lanes</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C104" s="8"/>
       <c r="F104" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-events-and-conditions</v>
-      </c>
-      <c r="B105" s="9" t="s">
-        <v>133</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/other-temporary-traffic-management-measures-or-plans</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>128</v>
       </c>
       <c r="C105" s="8"/>
-      <c r="E105" s="1" t="str">
-        <f>CONCATENATE(A106,", ",A107,", ",A108)</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/accidents-and-incidents, https://w3id.org/mobilitydcat-ap/mobility-theme/poor-road-conditions, https://w3id.org/mobilitydcat-ap/mobility-theme/road-weather-conditions</v>
-      </c>
       <c r="F105" s="1" t="str">
-        <f>A20</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/accidents-and-incidents</v>
-      </c>
-      <c r="B106" s="8" t="s">
-        <v>134</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-work-information</v>
+      </c>
+      <c r="B106" s="9" t="s">
+        <v>129</v>
       </c>
       <c r="C106" s="8"/>
+      <c r="E106" s="1" t="str">
+        <f>CONCATENATE(A107,", ",A108)</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/long-term-road-works, https://w3id.org/mobilitydcat-ap/mobility-theme/short-term-road-works</v>
+      </c>
       <c r="F106" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+        <f>A24</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/poor-road-conditions</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/long-term-road-works</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C107" s="8"/>
       <c r="F107" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>130</v>
+        <v>34</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-weather-conditions</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/short-term-road-works</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C108" s="8"/>
       <c r="F108" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="195" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A109" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/real-time-traffic-data</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-events-and-conditions</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C109" s="8"/>
-      <c r="E109" s="25" t="str">
-        <f>_xlfn.TEXTJOIN(", ",,A110:A121)</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/traffic-volume, https://w3id.org/mobilitydcat-ap/mobility-theme/speed, https://w3id.org/mobilitydcat-ap/mobility-theme/traffic-speed, https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-length-of-traffic-queues, https://w3id.org/mobilitydcat-ap/mobility-theme/current-travel-times, https://w3id.org/mobilitydcat-ap/mobility-theme/current-road-travel-times, https://w3id.org/mobilitydcat-ap/mobility-theme/predicted-travel-times, https://w3id.org/mobilitydcat-ap/mobility-theme/predicted-road-travel-times, https://w3id.org/mobilitydcat-ap/mobility-theme/expected-delays, https://w3id.org/mobilitydcat-ap/mobility-theme/expected-road-traffic-delays, https://w3id.org/mobilitydcat-ap/mobility-theme/waiting-time-at-border-crossings-to-non-eu-member-states, https://w3id.org/mobilitydcat-ap/mobility-theme/traffic-data-at-border-crossings-to-third-countries</v>
+      <c r="E109" s="1" t="str">
+        <f>CONCATENATE(A110,", ",A111,", ",A112)</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/accidents-and-incidents, https://w3id.org/mobilitydcat-ap/mobility-theme/poor-road-conditions, https://w3id.org/mobilitydcat-ap/mobility-theme/road-weather-conditions</v>
       </c>
       <c r="F109" s="1" t="str">
-        <f>A20</f>
+        <f>A24</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A110" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/traffic-volume</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/accidents-and-incidents</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C110" s="8"/>
       <c r="F110" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="15" t="str">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A111" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/poor-road-conditions</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C111" s="8"/>
+      <c r="F111" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A112" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-weather-conditions</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C112" s="8"/>
+      <c r="F112" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="165" x14ac:dyDescent="0.25">
+      <c r="A113" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/real-time-traffic-data</v>
+      </c>
+      <c r="B113" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C113" s="8"/>
+      <c r="E113" s="25" t="str">
+        <f>_xlfn.TEXTJOIN(", ",,A114:A125)</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/traffic-volume, https://w3id.org/mobilitydcat-ap/mobility-theme/speed, https://w3id.org/mobilitydcat-ap/mobility-theme/traffic-speed, https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-length-of-traffic-queues, https://w3id.org/mobilitydcat-ap/mobility-theme/current-travel-times, https://w3id.org/mobilitydcat-ap/mobility-theme/current-road-travel-times, https://w3id.org/mobilitydcat-ap/mobility-theme/predicted-travel-times, https://w3id.org/mobilitydcat-ap/mobility-theme/predicted-road-travel-times, https://w3id.org/mobilitydcat-ap/mobility-theme/expected-delays, https://w3id.org/mobilitydcat-ap/mobility-theme/expected-road-traffic-delays, https://w3id.org/mobilitydcat-ap/mobility-theme/waiting-time-at-border-crossings-to-non-eu-member-states, https://w3id.org/mobilitydcat-ap/mobility-theme/traffic-data-at-border-crossings-to-third-countries</v>
+      </c>
+      <c r="F113" s="1" t="str">
+        <f>A24</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/traffic-volume</v>
+      </c>
+      <c r="B114" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C114" s="8"/>
+      <c r="F114" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="15" t="str">
         <f t="shared" si="2"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/speed</v>
       </c>
-      <c r="B111" s="16" t="s">
+      <c r="B115" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="C111" s="16"/>
-      <c r="D111" s="17"/>
-      <c r="E111" s="17"/>
-      <c r="F111" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G111" s="18" t="b">
+      <c r="C115" s="16"/>
+      <c r="D115" s="17"/>
+      <c r="E115" s="17"/>
+      <c r="F115" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G115" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="H111" s="18" t="s">
+      <c r="H115" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="I111" s="17" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="20" t="str">
+      <c r="I115" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="20" t="str">
         <f t="shared" si="2"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/traffic-speed</v>
       </c>
-      <c r="B112" s="24" t="s">
+      <c r="B116" s="24" t="s">
         <v>141</v>
       </c>
-      <c r="C112" s="24"/>
-      <c r="D112" s="22"/>
-      <c r="E112" s="22"/>
-      <c r="F112" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H112" s="22"/>
-      <c r="I112" s="22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" s="10" t="str">
+      <c r="C116" s="24"/>
+      <c r="D116" s="22"/>
+      <c r="E116" s="22"/>
+      <c r="F116" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H116" s="22"/>
+      <c r="I116" s="22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="10" t="str">
         <f t="shared" si="2"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-length-of-traffic-queues</v>
       </c>
-      <c r="B113" s="8" t="s">
+      <c r="B117" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="C113" s="8"/>
-      <c r="F113" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I113" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="15" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B114,"/","-"))," ","-"),",",""))</f>
+      <c r="C117" s="8"/>
+      <c r="F117" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="15" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B118,"/","-"))," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/current-travel-times</v>
       </c>
-      <c r="B114" s="16" t="s">
+      <c r="B118" s="16" t="s">
         <v>143</v>
-      </c>
-      <c r="C114" s="16"/>
-      <c r="D114" s="17"/>
-      <c r="E114" s="17"/>
-      <c r="F114" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G114" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H114" s="17" t="str">
-        <f>A115</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/current-road-travel-times</v>
-      </c>
-      <c r="I114" s="18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="20" t="str">
-        <f t="shared" ref="A115:A119" si="3">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B115,"/","-"))," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/current-road-travel-times</v>
-      </c>
-      <c r="B115" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="C115" s="24"/>
-      <c r="D115" s="22"/>
-      <c r="E115" s="22"/>
-      <c r="F115" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H115" s="22"/>
-      <c r="I115" s="23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A116" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/predicted-travel-times</v>
-      </c>
-      <c r="B116" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="C116" s="16"/>
-      <c r="D116" s="17"/>
-      <c r="E116" s="17"/>
-      <c r="F116" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G116" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H116" s="17" t="str">
-        <f>A117</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/predicted-road-travel-times</v>
-      </c>
-      <c r="I116" s="17" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/predicted-road-travel-times</v>
-      </c>
-      <c r="B117" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="C117" s="24"/>
-      <c r="D117" s="22"/>
-      <c r="E117" s="22"/>
-      <c r="F117" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H117" s="22"/>
-      <c r="I117" s="23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A118" s="15" t="str">
-        <f t="shared" si="3"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/expected-delays</v>
-      </c>
-      <c r="B118" s="16" t="s">
-        <v>147</v>
       </c>
       <c r="C118" s="16"/>
       <c r="D118" s="17"/>
       <c r="E118" s="17"/>
       <c r="F118" s="17" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="G118" s="18" t="b">
@@ -3539,25 +3514,25 @@
       </c>
       <c r="H118" s="17" t="str">
         <f>A119</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/expected-road-traffic-delays</v>
-      </c>
-      <c r="I118" s="17" t="s">
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/current-road-travel-times</v>
+      </c>
+      <c r="I118" s="18" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="119" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="20" t="str">
-        <f t="shared" si="3"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/expected-road-traffic-delays</v>
+        <f t="shared" ref="A119:A123" si="3">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B119,"/","-"))," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/current-road-travel-times</v>
       </c>
       <c r="B119" s="24" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C119" s="24"/>
       <c r="D119" s="22"/>
       <c r="E119" s="22"/>
       <c r="F119" s="22" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="H119" s="22"/>
@@ -3565,286 +3540,286 @@
         <v>34</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/waiting-time-at-border-crossings-to-non-eu-member-states</v>
-      </c>
-      <c r="B120" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="C120" s="8"/>
-      <c r="F120" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I120" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/traffic-data-at-border-crossings-to-third-countries</v>
-      </c>
-      <c r="B121" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C121" s="8"/>
-      <c r="F121" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I121" s="25" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/general-information-for-trip-planning</v>
-      </c>
-      <c r="B122" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="C122" s="8"/>
-      <c r="E122" s="1" t="str">
-        <f>_xlfn.TEXTJOIN(", ",,A123:A129)</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/address-identifiers, https://w3id.org/mobilitydcat-ap/mobility-theme/topographic-places, https://w3id.org/mobilitydcat-ap/mobility-theme/points-of-interest, https://w3id.org/mobilitydcat-ap/mobility-theme/parameters-needed-to-calculate-environmental-factors, https://w3id.org/mobilitydcat-ap/mobility-theme/parameters-needed-to-calculate-costs, https://w3id.org/mobilitydcat-ap/mobility-theme/parameters-needed-to-calculate-energy-fuel-consumption, https://w3id.org/mobilitydcat-ap/mobility-theme/estimated-travel-times-for-multimodal-trip-planning</v>
-      </c>
-      <c r="F122" s="1" t="str">
-        <f>A20</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
-      </c>
-      <c r="I122" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/address-identifiers</v>
-      </c>
-      <c r="B123" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="C123" s="8"/>
-      <c r="F123" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I123" s="1" t="s">
-        <v>46</v>
+    <row r="120" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/predicted-travel-times</v>
+      </c>
+      <c r="B120" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="C120" s="16"/>
+      <c r="D120" s="17"/>
+      <c r="E120" s="17"/>
+      <c r="F120" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G120" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H120" s="17" t="str">
+        <f>A121</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/predicted-road-travel-times</v>
+      </c>
+      <c r="I120" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/predicted-road-travel-times</v>
+      </c>
+      <c r="B121" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="C121" s="24"/>
+      <c r="D121" s="22"/>
+      <c r="E121" s="22"/>
+      <c r="F121" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H121" s="22"/>
+      <c r="I121" s="23" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="15" t="str">
+        <f t="shared" si="3"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/expected-delays</v>
+      </c>
+      <c r="B122" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="C122" s="16"/>
+      <c r="D122" s="17"/>
+      <c r="E122" s="17"/>
+      <c r="F122" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G122" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H122" s="17" t="str">
+        <f>A123</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/expected-road-traffic-delays</v>
+      </c>
+      <c r="I122" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="20" t="str">
+        <f t="shared" si="3"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/expected-road-traffic-delays</v>
+      </c>
+      <c r="B123" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C123" s="24"/>
+      <c r="D123" s="22"/>
+      <c r="E123" s="22"/>
+      <c r="F123" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H123" s="22"/>
+      <c r="I123" s="23" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/topographic-places</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/waiting-time-at-border-crossings-to-non-eu-member-states</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C124" s="8"/>
       <c r="F124" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/points-of-interest</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/traffic-data-at-border-crossings-to-third-countries</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C125" s="8"/>
       <c r="F125" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I125" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I125" s="25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="10" t="str">
         <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/general-information-for-trip-planning</v>
+      </c>
+      <c r="B126" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C126" s="8"/>
+      <c r="E126" s="1" t="str">
+        <f>_xlfn.TEXTJOIN(", ",,A127:A133)</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/address-identifiers, https://w3id.org/mobilitydcat-ap/mobility-theme/topographic-places, https://w3id.org/mobilitydcat-ap/mobility-theme/points-of-interest, https://w3id.org/mobilitydcat-ap/mobility-theme/parameters-needed-to-calculate-environmental-factors, https://w3id.org/mobilitydcat-ap/mobility-theme/parameters-needed-to-calculate-costs, https://w3id.org/mobilitydcat-ap/mobility-theme/parameters-needed-to-calculate-energy-fuel-consumption, https://w3id.org/mobilitydcat-ap/mobility-theme/estimated-travel-times-for-multimodal-trip-planning</v>
+      </c>
+      <c r="F126" s="1" t="str">
+        <f>A24</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/address-identifiers</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C127" s="8"/>
+      <c r="F127" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/topographic-places</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C128" s="8"/>
+      <c r="F128" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/points-of-interest</v>
+      </c>
+      <c r="B129" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C129" s="8"/>
+      <c r="F129" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A130" s="10" t="str">
+        <f t="shared" si="2"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parameters-needed-to-calculate-environmental-factors</v>
       </c>
-      <c r="B126" s="8" t="s">
+      <c r="B130" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C126" s="8"/>
-      <c r="D126" s="1" t="s">
+      <c r="C130" s="8"/>
+      <c r="D130" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F126" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I126" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A127" s="15" t="str">
+      <c r="F130" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I130" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A131" s="15" t="str">
         <f t="shared" si="2"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parameters-needed-to-calculate-costs</v>
       </c>
-      <c r="B127" s="16" t="s">
+      <c r="B131" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="C127" s="16"/>
-      <c r="D127" s="17"/>
-      <c r="E127" s="17"/>
-      <c r="F127" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G127" s="18" t="b">
+      <c r="C131" s="16"/>
+      <c r="D131" s="17"/>
+      <c r="E131" s="17"/>
+      <c r="F131" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G131" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="H127" s="17" t="s">
+      <c r="H131" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="I127" s="17"/>
-    </row>
-    <row r="128" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A128" s="20" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B128,"/","-"))," ","-"),",",""))</f>
+      <c r="I131" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A132" s="20" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B132,"/","-"))," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parameters-needed-to-calculate-energy-fuel-consumption</v>
       </c>
-      <c r="B128" s="24" t="s">
+      <c r="B132" s="24" t="s">
         <v>159</v>
       </c>
-      <c r="C128" s="24"/>
-      <c r="D128" s="22" t="s">
+      <c r="C132" s="24"/>
+      <c r="D132" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="E128" s="22"/>
-      <c r="F128" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H128" s="22"/>
-      <c r="I128" s="22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A129" s="20" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B129,"/","-"))," ","-"),",",""))</f>
+      <c r="E132" s="22"/>
+      <c r="F132" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H132" s="22"/>
+      <c r="I132" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A133" s="20" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B133,"/","-"))," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/estimated-travel-times-for-multimodal-trip-planning</v>
       </c>
-      <c r="B129" s="21" t="s">
+      <c r="B133" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="C129" s="24"/>
-      <c r="D129" s="22" t="s">
+      <c r="C133" s="24"/>
+      <c r="D133" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="E129" s="22"/>
-      <c r="F129" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H129" s="22"/>
-      <c r="I129" s="22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" s="18" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="15" t="str">
-        <f t="shared" ref="A130" si="4">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B130,"/","-"))," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-scheduled-transport</v>
-      </c>
-      <c r="B130" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="C130" s="16"/>
-      <c r="D130" s="17"/>
-      <c r="E130" s="17"/>
-      <c r="F130" s="17" t="str">
-        <f>A20</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
-      </c>
-      <c r="G130" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H130" s="17" t="str">
-        <f>A131</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-on-demand-services</v>
-      </c>
-      <c r="I130" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" s="23" customFormat="1" ht="359.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>164</v>
-      </c>
-      <c r="B131" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="C131" s="24"/>
-      <c r="D131" s="22"/>
-      <c r="E131" s="22" t="str">
-        <f>_xlfn.TEXTJOIN(" ,",,A133:A174)</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-location-and-features ,https://w3id.org/mobilitydcat-ap/mobility-theme/stop-facilities-geometry-and-map-layout ,https://w3id.org/mobilitydcat-ap/mobility-theme/facility-geometry-and-map-layout ,https://w3id.org/mobilitydcat-ap/mobility-theme/stop-facilities-status-of-features ,https://w3id.org/mobilitydcat-ap/mobility-theme/facility-features-status ,https://w3id.org/mobilitydcat-ap/mobility-theme/stop-facilities-accessibility-and-paths-within-facility ,https://w3id.org/mobilitydcat-ap/mobility-theme/accessibility-and-paths-within-facilities ,https://w3id.org/mobilitydcat-ap/mobility-theme/operational-calendar ,https://w3id.org/mobilitydcat-ap/mobility-theme/connection-links ,https://w3id.org/mobilitydcat-ap/mobility-theme/network-topology-and-routes-lines ,https://w3id.org/mobilitydcat-ap/mobility-theme/transport-operators ,https://w3id.org/mobilitydcat-ap/mobility-theme/timetables-static ,https://w3id.org/mobilitydcat-ap/mobility-theme/real-time-estimated-departure-and-arrival-times ,https://w3id.org/mobilitydcat-ap/mobility-theme/planned-interchanges-between-scheduled-services ,https://w3id.org/mobilitydcat-ap/mobility-theme/hours-of-operation ,https://w3id.org/mobilitydcat-ap/mobility-theme/vehicle-details ,https://w3id.org/mobilitydcat-ap/mobility-theme/transport-operator-vehicle-fleet-description ,https://w3id.org/mobilitydcat-ap/mobility-theme/environmental-standards-for-vehicles ,https://w3id.org/mobilitydcat-ap/mobility-theme/disruptions-delays-cancellations ,https://w3id.org/mobilitydcat-ap/mobility-theme/basic-common-standard-fares ,https://w3id.org/mobilitydcat-ap/mobility-theme/passenger-classes ,https://w3id.org/mobilitydcat-ap/mobility-theme/common-fare-products ,https://w3id.org/mobilitydcat-ap/mobility-theme/special-fare-products ,https://w3id.org/mobilitydcat-ap/mobility-theme/basic-commercial-conditions ,https://w3id.org/mobilitydcat-ap/mobility-theme/purchase-information ,https://w3id.org/mobilitydcat-ap/mobility-theme/purchase-and-reservation-information ,https://w3id.org/mobilitydcat-ap/mobility-theme/defaut-transfer-times-at-interchanges ,https://w3id.org/mobilitydcat-ap/mobility-theme/default-transfer-times-at-interchanges ,https://w3id.org/mobilitydcat-ap/mobility-theme/existence-of-assistance-services ,https://w3id.org/mobilitydcat-ap/mobility-theme/historic-travel-and-traffic-data-and-delays ,https://w3id.org/mobilitydcat-ap/mobility-theme/observed-data-on-delays-and-passing-time ,https://w3id.org/mobilitydcat-ap/mobility-theme/observed-data-on-cancellations ,https://w3id.org/mobilitydcat-ap/mobility-theme/vehicle-occupancy ,https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-non-scheduled-transport ,https://w3id.org/mobilitydcat-ap/mobility-theme/provider-data ,https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-provider-data ,https://w3id.org/mobilitydcat-ap/mobility-theme/service-areas-and-service-times ,https://w3id.org/mobilitydcat-ap/mobility-theme/service-area ,https://w3id.org/mobilitydcat-ap/mobility-theme/locations-and-stations ,https://w3id.org/mobilitydcat-ap/mobility-theme/fares ,https://w3id.org/mobilitydcat-ap/mobility-theme/reservation-and-purchase-options ,https://w3id.org/mobilitydcat-ap/mobility-theme/accessibility-information-for-vehicles</v>
-      </c>
-      <c r="F131" s="22" t="str">
-        <f>A20</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
-      </c>
-      <c r="H131" s="22"/>
-      <c r="I131" s="22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A132" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/stop-facilities-location-and-features</v>
-      </c>
-      <c r="B132" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="C132" s="16"/>
-      <c r="D132" s="17"/>
-      <c r="E132" s="17"/>
-      <c r="F132" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G132" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H132" s="17" t="str">
-        <f>A133</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-location-and-features</v>
-      </c>
-      <c r="I132" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-location-and-features</v>
-      </c>
-      <c r="B133" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="C133" s="24"/>
-      <c r="D133" s="22"/>
       <c r="E133" s="22"/>
       <c r="F133" s="22" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="H133" s="22"/>
@@ -3852,46 +3827,48 @@
         <v>46</v>
       </c>
     </row>
-    <row r="134" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" s="18" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/stop-facilities-geometry-and-map-layout</v>
+        <f t="shared" ref="A134" si="4">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B134,"/","-"))," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-scheduled-transport</v>
       </c>
       <c r="B134" s="16" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C134" s="16"/>
       <c r="D134" s="17"/>
       <c r="E134" s="17"/>
       <c r="F134" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+        <f>A24</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
       <c r="G134" s="18" t="b">
         <v>1</v>
       </c>
       <c r="H134" s="17" t="str">
         <f>A135</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-geometry-and-map-layout</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-on-demand-services</v>
       </c>
       <c r="I134" s="17" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="135" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-geometry-and-map-layout</v>
-      </c>
-      <c r="B135" s="24" t="s">
-        <v>169</v>
+    <row r="135" spans="1:9" s="23" customFormat="1" ht="359.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>164</v>
+      </c>
+      <c r="B135" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="C135" s="24"/>
       <c r="D135" s="22"/>
-      <c r="E135" s="22"/>
+      <c r="E135" s="22" t="str">
+        <f>_xlfn.TEXTJOIN(" ,",,A137:A178)</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-location-and-features ,https://w3id.org/mobilitydcat-ap/mobility-theme/stop-facilities-geometry-and-map-layout ,https://w3id.org/mobilitydcat-ap/mobility-theme/facility-geometry-and-map-layout ,https://w3id.org/mobilitydcat-ap/mobility-theme/stop-facilities-status-of-features ,https://w3id.org/mobilitydcat-ap/mobility-theme/facility-features-status ,https://w3id.org/mobilitydcat-ap/mobility-theme/stop-facilities-accessibility-and-paths-within-facility ,https://w3id.org/mobilitydcat-ap/mobility-theme/accessibility-and-paths-within-facilities ,https://w3id.org/mobilitydcat-ap/mobility-theme/operational-calendar ,https://w3id.org/mobilitydcat-ap/mobility-theme/connection-links ,https://w3id.org/mobilitydcat-ap/mobility-theme/network-topology-and-routes-lines ,https://w3id.org/mobilitydcat-ap/mobility-theme/transport-operators ,https://w3id.org/mobilitydcat-ap/mobility-theme/timetables-static ,https://w3id.org/mobilitydcat-ap/mobility-theme/real-time-estimated-departure-and-arrival-times ,https://w3id.org/mobilitydcat-ap/mobility-theme/planned-interchanges-between-scheduled-services ,https://w3id.org/mobilitydcat-ap/mobility-theme/hours-of-operation ,https://w3id.org/mobilitydcat-ap/mobility-theme/vehicle-details ,https://w3id.org/mobilitydcat-ap/mobility-theme/transport-operator-vehicle-fleet-description ,https://w3id.org/mobilitydcat-ap/mobility-theme/environmental-standards-for-vehicles ,https://w3id.org/mobilitydcat-ap/mobility-theme/disruptions-delays-cancellations ,https://w3id.org/mobilitydcat-ap/mobility-theme/basic-common-standard-fares ,https://w3id.org/mobilitydcat-ap/mobility-theme/passenger-classes ,https://w3id.org/mobilitydcat-ap/mobility-theme/common-fare-products ,https://w3id.org/mobilitydcat-ap/mobility-theme/special-fare-products ,https://w3id.org/mobilitydcat-ap/mobility-theme/basic-commercial-conditions ,https://w3id.org/mobilitydcat-ap/mobility-theme/purchase-information ,https://w3id.org/mobilitydcat-ap/mobility-theme/purchase-and-reservation-information ,https://w3id.org/mobilitydcat-ap/mobility-theme/defaut-transfer-times-at-interchanges ,https://w3id.org/mobilitydcat-ap/mobility-theme/default-transfer-times-at-interchanges ,https://w3id.org/mobilitydcat-ap/mobility-theme/existence-of-assistance-services ,https://w3id.org/mobilitydcat-ap/mobility-theme/historic-travel-and-traffic-data-and-delays ,https://w3id.org/mobilitydcat-ap/mobility-theme/observed-data-on-delays-and-passing-time ,https://w3id.org/mobilitydcat-ap/mobility-theme/observed-data-on-cancellations ,https://w3id.org/mobilitydcat-ap/mobility-theme/vehicle-occupancy ,https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-non-scheduled-transport ,https://w3id.org/mobilitydcat-ap/mobility-theme/provider-data ,https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-provider-data ,https://w3id.org/mobilitydcat-ap/mobility-theme/service-areas-and-service-times ,https://w3id.org/mobilitydcat-ap/mobility-theme/service-area ,https://w3id.org/mobilitydcat-ap/mobility-theme/locations-and-stations ,https://w3id.org/mobilitydcat-ap/mobility-theme/fares ,https://w3id.org/mobilitydcat-ap/mobility-theme/reservation-and-purchase-options ,https://w3id.org/mobilitydcat-ap/mobility-theme/accessibility-information-for-vehicles</v>
+      </c>
       <c r="F135" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+        <f>A24</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
       <c r="H135" s="22"/>
       <c r="I135" s="22" t="s">
@@ -3901,16 +3878,16 @@
     <row r="136" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="15" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/stop-facilities-status-of-features</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/stop-facilities-location-and-features</v>
       </c>
       <c r="B136" s="16" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C136" s="16"/>
       <c r="D136" s="17"/>
       <c r="E136" s="17"/>
       <c r="F136" s="17" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="G136" s="18" t="b">
@@ -3918,7 +3895,7 @@
       </c>
       <c r="H136" s="17" t="str">
         <f>A137</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-features-status</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-location-and-features</v>
       </c>
       <c r="I136" s="17" t="s">
         <v>46</v>
@@ -3927,42 +3904,44 @@
     <row r="137" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-features-status</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-location-and-features</v>
       </c>
       <c r="B137" s="24" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C137" s="24"/>
       <c r="D137" s="22"/>
       <c r="E137" s="22"/>
       <c r="F137" s="22" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="H137" s="22"/>
-      <c r="I137" s="22"/>
+      <c r="I137" s="22" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="138" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="15" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/stop-facilities-accessibility-and-paths-within-facility</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/stop-facilities-geometry-and-map-layout</v>
       </c>
       <c r="B138" s="16" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C138" s="16"/>
       <c r="D138" s="17"/>
       <c r="E138" s="17"/>
       <c r="F138" s="17" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="G138" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="H138" s="18" t="str">
+      <c r="H138" s="17" t="str">
         <f>A139</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/accessibility-and-paths-within-facilities</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-geometry-and-map-layout</v>
       </c>
       <c r="I138" s="17" t="s">
         <v>46</v>
@@ -3971,100 +3950,126 @@
     <row r="139" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="20" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/accessibility-and-paths-within-facilities</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-geometry-and-map-layout</v>
       </c>
       <c r="B139" s="24" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C139" s="24"/>
       <c r="D139" s="22"/>
       <c r="E139" s="22"/>
       <c r="F139" s="22" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="H139" s="22"/>
-      <c r="I139" s="22"/>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A140" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/operational-calendar</v>
-      </c>
-      <c r="B140" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="C140" s="8"/>
-      <c r="F140" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I140" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A141" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/connection-links</v>
-      </c>
-      <c r="B141" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="C141" s="8"/>
-      <c r="F141" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I141" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A142" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/network-topology-and-routes-lines</v>
-      </c>
-      <c r="B142" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="C142" s="8"/>
-      <c r="F142" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I142" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A143" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/transport-operators</v>
-      </c>
-      <c r="B143" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="C143" s="8"/>
-      <c r="F143" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I143" s="1" t="s">
+      <c r="I139" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/stop-facilities-status-of-features</v>
+      </c>
+      <c r="B140" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="C140" s="16"/>
+      <c r="D140" s="17"/>
+      <c r="E140" s="17"/>
+      <c r="F140" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G140" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H140" s="17" t="str">
+        <f>A141</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-features-status</v>
+      </c>
+      <c r="I140" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-features-status</v>
+      </c>
+      <c r="B141" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="C141" s="24"/>
+      <c r="D141" s="22"/>
+      <c r="E141" s="22"/>
+      <c r="F141" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H141" s="22"/>
+      <c r="I141" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/stop-facilities-accessibility-and-paths-within-facility</v>
+      </c>
+      <c r="B142" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="C142" s="16"/>
+      <c r="D142" s="17"/>
+      <c r="E142" s="17"/>
+      <c r="F142" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G142" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H142" s="18" t="str">
+        <f>A143</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/accessibility-and-paths-within-facilities</v>
+      </c>
+      <c r="I142" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/accessibility-and-paths-within-facilities</v>
+      </c>
+      <c r="B143" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="C143" s="24"/>
+      <c r="D143" s="22"/>
+      <c r="E143" s="22"/>
+      <c r="F143" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H143" s="22"/>
+      <c r="I143" s="22" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/timetables-static</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/operational-calendar</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C144" s="8"/>
       <c r="F144" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I144" s="1" t="s">
@@ -4074,14 +4079,14 @@
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/real-time-estimated-departure-and-arrival-times</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/connection-links</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C145" s="8"/>
       <c r="F145" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I145" s="1" t="s">
@@ -4091,405 +4096,394 @@
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/planned-interchanges-between-scheduled-services</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/network-topology-and-routes-lines</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C146" s="8"/>
       <c r="F146" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/hours-of-operation</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/transport-operators</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C147" s="8"/>
-      <c r="D147" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="F147" s="1" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="148" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A148" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/vehicle-details</v>
-      </c>
-      <c r="B148" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="C148" s="16"/>
-      <c r="D148" s="17"/>
-      <c r="E148" s="17"/>
-      <c r="F148" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G148" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H148" s="17" t="str">
-        <f>A149</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/transport-operator-vehicle-fleet-description</v>
-      </c>
-      <c r="I148" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A149" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/transport-operator-vehicle-fleet-description</v>
-      </c>
-      <c r="B149" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="C149" s="24"/>
-      <c r="D149" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="E149" s="22"/>
-      <c r="F149" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H149" s="22"/>
-      <c r="I149" s="22"/>
-    </row>
-    <row r="150" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A150" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/environmental-standards-for-vehicles</v>
-      </c>
-      <c r="B150" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="C150" s="16"/>
-      <c r="D150" s="17"/>
-      <c r="E150" s="17"/>
-      <c r="F150" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G150" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H150" s="17" t="str">
-        <f>A149</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/transport-operator-vehicle-fleet-description</v>
-      </c>
-      <c r="I150" s="17" t="s">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/timetables-static</v>
+      </c>
+      <c r="B148" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C148" s="8"/>
+      <c r="F148" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/real-time-estimated-departure-and-arrival-times</v>
+      </c>
+      <c r="B149" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="C149" s="8"/>
+      <c r="F149" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/planned-interchanges-between-scheduled-services</v>
+      </c>
+      <c r="B150" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C150" s="8"/>
+      <c r="F150" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I150" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="10" t="str">
-        <f t="shared" ref="A151:A196" si="5">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B151,"/","-"))," ","-"),",",""))</f>
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/hours-of-operation</v>
+      </c>
+      <c r="B151" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C151" s="8"/>
+      <c r="D151" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F151" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/vehicle-details</v>
+      </c>
+      <c r="B152" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="C152" s="16"/>
+      <c r="D152" s="17"/>
+      <c r="E152" s="17"/>
+      <c r="F152" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G152" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H152" s="17" t="str">
+        <f>A153</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/transport-operator-vehicle-fleet-description</v>
+      </c>
+      <c r="I152" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A153" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/transport-operator-vehicle-fleet-description</v>
+      </c>
+      <c r="B153" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="C153" s="24"/>
+      <c r="D153" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="E153" s="22"/>
+      <c r="F153" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H153" s="22"/>
+      <c r="I153" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/environmental-standards-for-vehicles</v>
+      </c>
+      <c r="B154" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C154" s="16"/>
+      <c r="D154" s="17"/>
+      <c r="E154" s="17"/>
+      <c r="F154" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G154" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H154" s="17" t="str">
+        <f>A153</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/transport-operator-vehicle-fleet-description</v>
+      </c>
+      <c r="I154" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="10" t="str">
+        <f t="shared" ref="A155:A200" si="5">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B155,"/","-"))," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/disruptions-delays-cancellations</v>
       </c>
-      <c r="B151" s="8" t="s">
+      <c r="B155" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="C151" s="8"/>
-      <c r="F151" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I151" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A152" s="10" t="str">
+      <c r="C155" s="8"/>
+      <c r="F155" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="10" t="str">
         <f t="shared" si="5"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/basic-common-standard-fares</v>
       </c>
-      <c r="B152" s="8" t="s">
+      <c r="B156" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="C152" s="8"/>
-      <c r="F152" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I152" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A153" s="10" t="str">
+      <c r="C156" s="8"/>
+      <c r="F156" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" s="10" t="str">
         <f t="shared" si="5"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/passenger-classes</v>
       </c>
-      <c r="B153" s="8" t="s">
+      <c r="B157" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="C153" s="8"/>
-      <c r="F153" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I153" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A154" s="10" t="str">
+      <c r="C157" s="8"/>
+      <c r="F157" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I157" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="10" t="str">
         <f t="shared" si="5"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/common-fare-products</v>
       </c>
-      <c r="B154" s="8" t="s">
+      <c r="B158" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="C154" s="8"/>
-      <c r="F154" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I154" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A155" s="10" t="str">
+      <c r="C158" s="8"/>
+      <c r="F158" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" s="10" t="str">
         <f t="shared" si="5"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/special-fare-products</v>
       </c>
-      <c r="B155" s="8" t="s">
+      <c r="B159" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="C155" s="8"/>
-      <c r="F155" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I155" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A156" s="10" t="str">
+      <c r="C159" s="8"/>
+      <c r="F159" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A160" s="10" t="str">
         <f t="shared" si="5"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/basic-commercial-conditions</v>
       </c>
-      <c r="B156" s="8" t="s">
+      <c r="B160" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="C156" s="8"/>
-      <c r="D156" s="1" t="s">
+      <c r="C160" s="8"/>
+      <c r="D160" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="F156" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I156" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A157" s="15" t="str">
+      <c r="F160" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="15" t="str">
         <f t="shared" si="5"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/purchase-information</v>
       </c>
-      <c r="B157" s="16" t="s">
+      <c r="B161" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="C157" s="16"/>
-      <c r="D157" s="17"/>
-      <c r="E157" s="17"/>
-      <c r="F157" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G157" s="18" t="b">
+      <c r="C161" s="16"/>
+      <c r="D161" s="17"/>
+      <c r="E161" s="17"/>
+      <c r="F161" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G161" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="H157" s="17" t="str">
-        <f>A158</f>
+      <c r="H161" s="17" t="str">
+        <f>A162</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/purchase-and-reservation-information</v>
       </c>
-      <c r="I157" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/purchase-and-reservation-information</v>
-      </c>
-      <c r="B158" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="C158" s="24"/>
-      <c r="D158" s="22"/>
-      <c r="E158" s="22"/>
-      <c r="F158" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H158" s="22"/>
-      <c r="I158" s="23" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A159" s="15" t="str">
-        <f t="shared" ref="A159" si="6">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B159,"/","-"))," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/defaut-transfer-times-at-interchanges</v>
-      </c>
-      <c r="B159" s="32" t="s">
-        <v>196</v>
-      </c>
-      <c r="C159" s="16"/>
-      <c r="D159" s="17"/>
-      <c r="E159" s="17"/>
-      <c r="F159" s="17" t="str">
-        <f>A20</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
-      </c>
-      <c r="G159" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H159" s="17" t="str">
-        <f>A160</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/default-transfer-times-at-interchanges</v>
-      </c>
-      <c r="I159" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/default-transfer-times-at-interchanges</v>
-      </c>
-      <c r="B160" s="30" t="s">
-        <v>197</v>
-      </c>
-      <c r="C160" s="24"/>
-      <c r="D160" s="22"/>
-      <c r="E160" s="22"/>
-      <c r="F160" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H160" s="22"/>
-      <c r="I160" s="23" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A161" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/existence-of-assistance-services</v>
-      </c>
-      <c r="B161" s="30" t="s">
-        <v>198</v>
-      </c>
-      <c r="C161" s="24"/>
-      <c r="D161" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="E161" s="22"/>
-      <c r="F161" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H161" s="22"/>
-      <c r="I161" s="22" t="s">
+      <c r="I161" s="17" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="162" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="20" t="str">
         <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/historic-travel-and-traffic-data-and-delays</v>
-      </c>
-      <c r="B162" s="30" t="s">
-        <v>200</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/purchase-and-reservation-information</v>
+      </c>
+      <c r="B162" s="24" t="s">
+        <v>195</v>
       </c>
       <c r="C162" s="24"/>
       <c r="D162" s="22"/>
       <c r="E162" s="22"/>
       <c r="F162" s="22" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="H162" s="22"/>
-      <c r="I162" s="22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/observed-data-on-delays-and-passing-time</v>
-      </c>
-      <c r="B163" s="30" t="s">
-        <v>201</v>
-      </c>
-      <c r="C163" s="24"/>
-      <c r="D163" s="22"/>
-      <c r="E163" s="22"/>
-      <c r="F163" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H163" s="22"/>
-      <c r="I163" s="22" t="s">
+      <c r="I162" s="23" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="15" t="str">
+        <f t="shared" ref="A163" si="6">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B163,"/","-"))," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/defaut-transfer-times-at-interchanges</v>
+      </c>
+      <c r="B163" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="C163" s="16"/>
+      <c r="D163" s="17"/>
+      <c r="E163" s="17"/>
+      <c r="F163" s="17" t="str">
+        <f>A24</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
+      </c>
+      <c r="G163" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H163" s="17" t="str">
+        <f>A164</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/default-transfer-times-at-interchanges</v>
+      </c>
+      <c r="I163" s="18" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="164" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="20" t="str">
         <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/observed-data-on-cancellations</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/default-transfer-times-at-interchanges</v>
       </c>
       <c r="B164" s="30" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C164" s="24"/>
       <c r="D164" s="22"/>
       <c r="E164" s="22"/>
       <c r="F164" s="22" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="H164" s="22"/>
-      <c r="I164" s="22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A165" s="23" t="s">
-        <v>203</v>
+      <c r="I164" s="23" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/existence-of-assistance-services</v>
       </c>
       <c r="B165" s="30" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C165" s="24"/>
       <c r="D165" s="22" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E165" s="22"/>
       <c r="F165" s="22" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="H165" s="22"/>
@@ -4497,70 +4491,59 @@
         <v>46</v>
       </c>
     </row>
-    <row r="166" spans="1:9" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="15" t="str">
-        <f t="shared" ref="A166" si="7">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B166,"/","-"))," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-non-scheduled-transport</v>
-      </c>
-      <c r="B166" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="C166" s="16"/>
-      <c r="D166" s="17"/>
-      <c r="E166" s="17"/>
-      <c r="F166" s="17" t="str">
-        <f>A20</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
-      </c>
-      <c r="G166" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H166" s="17" t="str">
-        <f>A131</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-on-demand-services</v>
-      </c>
-      <c r="I166" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="15" t="str">
+    <row r="166" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="20" t="str">
         <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/provider-data</v>
-      </c>
-      <c r="B167" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="C167" s="16"/>
-      <c r="D167" s="17"/>
-      <c r="E167" s="17"/>
-      <c r="F167" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G167" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H167" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="I167" s="17" t="s">
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/historic-travel-and-traffic-data-and-delays</v>
+      </c>
+      <c r="B166" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="C166" s="24"/>
+      <c r="D166" s="22"/>
+      <c r="E166" s="22"/>
+      <c r="F166" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H166" s="22"/>
+      <c r="I166" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/observed-data-on-delays-and-passing-time</v>
+      </c>
+      <c r="B167" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="C167" s="24"/>
+      <c r="D167" s="22"/>
+      <c r="E167" s="22"/>
+      <c r="F167" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H167" s="22"/>
+      <c r="I167" s="22" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="168" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="20" t="str">
         <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-provider-data</v>
-      </c>
-      <c r="B168" s="24" t="s">
-        <v>209</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/observed-data-on-cancellations</v>
+      </c>
+      <c r="B168" s="30" t="s">
+        <v>202</v>
       </c>
       <c r="C168" s="24"/>
       <c r="D168" s="22"/>
       <c r="E168" s="22"/>
       <c r="F168" s="22" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="H168" s="22"/>
@@ -4568,657 +4551,753 @@
         <v>46</v>
       </c>
     </row>
-    <row r="169" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A169" s="15" t="str">
-        <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-areas-and-service-times</v>
-      </c>
-      <c r="B169" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="C169" s="16"/>
-      <c r="D169" s="17"/>
-      <c r="E169" s="17"/>
-      <c r="F169" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G169" s="18" t="b">
+    <row r="169" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="B169" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="C169" s="24"/>
+      <c r="D169" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="E169" s="22"/>
+      <c r="F169" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H169" s="22"/>
+      <c r="I169" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="15" t="str">
+        <f t="shared" ref="A170" si="7">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B170,"/","-"))," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-non-scheduled-transport</v>
+      </c>
+      <c r="B170" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="C170" s="16"/>
+      <c r="D170" s="17"/>
+      <c r="E170" s="17"/>
+      <c r="F170" s="17" t="str">
+        <f>A24</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
+      </c>
+      <c r="G170" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="H169" s="17" t="str">
-        <f>_xlfn.CONCAT(A170, ", ",A147)</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-area, https://w3id.org/mobilitydcat-ap/mobility-theme/hours-of-operation</v>
-      </c>
-      <c r="I169" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-area</v>
-      </c>
-      <c r="B170" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="C170" s="24"/>
-      <c r="D170" s="22"/>
-      <c r="E170" s="22"/>
-      <c r="F170" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H170" s="22"/>
-      <c r="I170" s="31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="H170" s="17" t="str">
+        <f>A135</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-on-demand-services</v>
+      </c>
+      <c r="I170" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="15" t="str">
         <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/locations-and-stations</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/provider-data</v>
       </c>
       <c r="B171" s="16" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C171" s="16"/>
       <c r="D171" s="17"/>
       <c r="E171" s="17"/>
       <c r="F171" s="17" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="G171" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="H171" s="17" t="str">
-        <f>A133</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-location-and-features</v>
-      </c>
-      <c r="I171" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9" s="18" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A172" s="15" t="str">
+      <c r="H171" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="I171" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="20" t="str">
         <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/fares</v>
-      </c>
-      <c r="B172" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="C172" s="16"/>
-      <c r="D172" s="17"/>
-      <c r="E172" s="17"/>
-      <c r="F172" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G172" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H172" s="17" t="str">
-        <f>_xlfn.CONCAT(A153, ", ", _xlfn.TEXTJOIN(", ",,A154:A156))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/passenger-classes, https://w3id.org/mobilitydcat-ap/mobility-theme/common-fare-products, https://w3id.org/mobilitydcat-ap/mobility-theme/special-fare-products, https://w3id.org/mobilitydcat-ap/mobility-theme/basic-commercial-conditions</v>
-      </c>
-      <c r="I172" s="17" t="s">
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-provider-data</v>
+      </c>
+      <c r="B172" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="C172" s="24"/>
+      <c r="D172" s="22"/>
+      <c r="E172" s="22"/>
+      <c r="F172" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H172" s="22"/>
+      <c r="I172" s="22" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="173" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A173" s="15" t="str">
         <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/reservation-and-purchase-options</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-areas-and-service-times</v>
       </c>
       <c r="B173" s="16" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C173" s="16"/>
       <c r="D173" s="17"/>
       <c r="E173" s="17"/>
       <c r="F173" s="17" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="G173" s="18" t="b">
         <v>1</v>
       </c>
       <c r="H173" s="17" t="str">
-        <f>A158</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/purchase-and-reservation-information</v>
+        <f>_xlfn.CONCAT(A174, ", ",A151)</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-area, https://w3id.org/mobilitydcat-ap/mobility-theme/hours-of-operation</v>
       </c>
       <c r="I173" s="17" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A174" s="10" t="str">
+    <row r="174" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="20" t="str">
         <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/accessibility-information-for-vehicles</v>
-      </c>
-      <c r="B174" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="C174" s="8"/>
-      <c r="F174" s="1" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="I174" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="175" spans="1:9" s="18" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-area</v>
+      </c>
+      <c r="B174" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="C174" s="24"/>
+      <c r="D174" s="22"/>
+      <c r="E174" s="22"/>
+      <c r="F174" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H174" s="22"/>
+      <c r="I174" s="31" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="15" t="str">
         <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/sharing-and-hiring-services</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/locations-and-stations</v>
       </c>
       <c r="B175" s="16" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C175" s="16"/>
       <c r="D175" s="17"/>
       <c r="E175" s="17"/>
       <c r="F175" s="17" t="str">
-        <f>A20</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
-      </c>
-      <c r="H175" s="17"/>
-      <c r="I175" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="176" spans="1:9" s="23" customFormat="1" ht="198" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="20" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G175" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H175" s="17" t="str">
+        <f>A137</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-location-and-features</v>
+      </c>
+      <c r="I175" s="18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" s="18" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A176" s="15" t="str">
         <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/sharing-hiring-and-renting-services</v>
-      </c>
-      <c r="B176" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="C176" s="24"/>
-      <c r="D176" s="22"/>
-      <c r="E176" s="22" t="str">
-        <f>_xlfn.TEXTJOIN(", ",,A177:A193)</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bike-sharing-locations-and-stations, https://w3id.org/mobilitydcat-ap/mobility-theme/car-sharing-locations-and-stations, https://w3id.org/mobilitydcat-ap/mobility-theme/bike-hiring-stations, https://w3id.org/mobilitydcat-ap/mobility-theme/car-hiring-stations, https://w3id.org/mobilitydcat-ap/mobility-theme/e-scooter-sharing-locations-and-stations, https://w3id.org/mobilitydcat-ap/mobility-theme/car-sharing-availability, https://w3id.org/mobilitydcat-ap/mobility-theme/bike-sharing-availability, https://w3id.org/mobilitydcat-ap/mobility-theme/car-hiring-availability, https://w3id.org/mobilitydcat-ap/mobility-theme/bike-hiring-availability, https://w3id.org/mobilitydcat-ap/mobility-theme/e-scooter-sharing-availability, https://w3id.org/mobilitydcat-ap/mobility-theme/service-locations-and-stations, https://w3id.org/mobilitydcat-ap/mobility-theme/service-vehicle-fleet-description, https://w3id.org/mobilitydcat-ap/mobility-theme/service-real-time-availability, https://w3id.org/mobilitydcat-ap/mobility-theme/service-payment-methods, https://w3id.org/mobilitydcat-ap/mobility-theme/service-zones, https://w3id.org/mobilitydcat-ap/mobility-theme/payment-methods, https://w3id.org/mobilitydcat-ap/mobility-theme/environmental-standards-for-vehicles</v>
-      </c>
-      <c r="F176" s="22" t="str">
-        <f>A20</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
-      </c>
-      <c r="H176" s="22"/>
-      <c r="I176" s="22"/>
-    </row>
-    <row r="177" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/fares</v>
+      </c>
+      <c r="B176" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="C176" s="16"/>
+      <c r="D176" s="17"/>
+      <c r="E176" s="17"/>
+      <c r="F176" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G176" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H176" s="17" t="str">
+        <f>_xlfn.CONCAT(A157, ", ", _xlfn.TEXTJOIN(", ",,A158:A160))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/passenger-classes, https://w3id.org/mobilitydcat-ap/mobility-theme/common-fare-products, https://w3id.org/mobilitydcat-ap/mobility-theme/special-fare-products, https://w3id.org/mobilitydcat-ap/mobility-theme/basic-commercial-conditions</v>
+      </c>
+      <c r="I176" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="15" t="str">
         <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bike-sharing-locations-and-stations</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/reservation-and-purchase-options</v>
       </c>
       <c r="B177" s="16" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C177" s="16"/>
       <c r="D177" s="17"/>
       <c r="E177" s="17"/>
       <c r="F177" s="17" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="G177" s="18" t="b">
         <v>1</v>
       </c>
       <c r="H177" s="17" t="str">
-        <f>A187</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-locations-and-stations</v>
-      </c>
-      <c r="I177" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A178" s="15" t="str">
+        <f>A162</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/purchase-and-reservation-information</v>
+      </c>
+      <c r="I177" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" s="10" t="str">
         <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/car-sharing-locations-and-stations</v>
-      </c>
-      <c r="B178" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="C178" s="16"/>
-      <c r="D178" s="17"/>
-      <c r="E178" s="17"/>
-      <c r="F178" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G178" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H178" s="17" t="str">
-        <f>A187</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-locations-and-stations</v>
-      </c>
-      <c r="I178" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/accessibility-information-for-vehicles</v>
+      </c>
+      <c r="B178" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="C178" s="8"/>
+      <c r="F178" s="1" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="I178" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" s="18" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="15" t="str">
         <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bike-hiring-stations</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/sharing-and-hiring-services</v>
       </c>
       <c r="B179" s="16" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C179" s="16"/>
       <c r="D179" s="17"/>
       <c r="E179" s="17"/>
       <c r="F179" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G179" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H179" s="17" t="str">
-        <f>A187</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-locations-and-stations</v>
-      </c>
+        <f>A24</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
+      </c>
+      <c r="H179" s="17"/>
       <c r="I179" s="17" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="180" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A180" s="15" t="str">
+    <row r="180" spans="1:9" s="23" customFormat="1" ht="198" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="20" t="str">
         <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/car-hiring-stations</v>
-      </c>
-      <c r="B180" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="C180" s="16"/>
-      <c r="D180" s="17"/>
-      <c r="E180" s="17"/>
-      <c r="F180" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G180" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H180" s="17" t="str">
-        <f>A187</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-locations-and-stations</v>
-      </c>
-      <c r="I180" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/sharing-hiring-and-renting-services</v>
+      </c>
+      <c r="B180" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="C180" s="24"/>
+      <c r="D180" s="22"/>
+      <c r="E180" s="22" t="str">
+        <f>_xlfn.TEXTJOIN(", ",,A181:A197)</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bike-sharing-locations-and-stations, https://w3id.org/mobilitydcat-ap/mobility-theme/car-sharing-locations-and-stations, https://w3id.org/mobilitydcat-ap/mobility-theme/bike-hiring-stations, https://w3id.org/mobilitydcat-ap/mobility-theme/car-hiring-stations, https://w3id.org/mobilitydcat-ap/mobility-theme/e-scooter-sharing-locations-and-stations, https://w3id.org/mobilitydcat-ap/mobility-theme/car-sharing-availability, https://w3id.org/mobilitydcat-ap/mobility-theme/bike-sharing-availability, https://w3id.org/mobilitydcat-ap/mobility-theme/car-hiring-availability, https://w3id.org/mobilitydcat-ap/mobility-theme/bike-hiring-availability, https://w3id.org/mobilitydcat-ap/mobility-theme/e-scooter-sharing-availability, https://w3id.org/mobilitydcat-ap/mobility-theme/service-locations-and-stations, https://w3id.org/mobilitydcat-ap/mobility-theme/service-vehicle-fleet-description, https://w3id.org/mobilitydcat-ap/mobility-theme/service-real-time-availability, https://w3id.org/mobilitydcat-ap/mobility-theme/service-payment-methods, https://w3id.org/mobilitydcat-ap/mobility-theme/service-zones, https://w3id.org/mobilitydcat-ap/mobility-theme/payment-methods, https://w3id.org/mobilitydcat-ap/mobility-theme/environmental-standards-for-vehicles</v>
+      </c>
+      <c r="F180" s="22" t="str">
+        <f>A24</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
+      </c>
+      <c r="H180" s="22"/>
+      <c r="I180" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="15" t="str">
         <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/e-scooter-sharing-locations-and-stations</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bike-sharing-locations-and-stations</v>
       </c>
       <c r="B181" s="16" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C181" s="16"/>
       <c r="D181" s="17"/>
       <c r="E181" s="17"/>
       <c r="F181" s="17" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="G181" s="18" t="b">
         <v>1</v>
       </c>
       <c r="H181" s="17" t="str">
-        <f>A187</f>
+        <f>A191</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-locations-and-stations</v>
       </c>
-      <c r="I181" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" s="18" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I181" s="18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="15" t="str">
         <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/car-sharing-availability</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/car-sharing-locations-and-stations</v>
       </c>
       <c r="B182" s="16" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C182" s="16"/>
       <c r="D182" s="17"/>
       <c r="E182" s="17"/>
       <c r="F182" s="17" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="G182" s="18" t="b">
         <v>1</v>
       </c>
       <c r="H182" s="17" t="str">
-        <f>_xlfn.TEXTJOIN(", ",,A188,A189)</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-vehicle-fleet-description, https://w3id.org/mobilitydcat-ap/mobility-theme/service-real-time-availability</v>
+        <f>A191</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-locations-and-stations</v>
       </c>
       <c r="I182" s="17" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="183" spans="1:9" s="18" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="15" t="str">
         <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bike-sharing-availability</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bike-hiring-stations</v>
       </c>
       <c r="B183" s="16" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C183" s="16"/>
       <c r="D183" s="17"/>
       <c r="E183" s="17"/>
       <c r="F183" s="17" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="G183" s="18" t="b">
         <v>1</v>
       </c>
       <c r="H183" s="17" t="str">
-        <f>_xlfn.TEXTJOIN(", ",,A188,A189)</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-vehicle-fleet-description, https://w3id.org/mobilitydcat-ap/mobility-theme/service-real-time-availability</v>
+        <f>A191</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-locations-and-stations</v>
       </c>
       <c r="I183" s="17" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="184" spans="1:9" s="18" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="15" t="str">
         <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/car-hiring-availability</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/car-hiring-stations</v>
       </c>
       <c r="B184" s="16" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C184" s="16"/>
       <c r="D184" s="17"/>
       <c r="E184" s="17"/>
       <c r="F184" s="17" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="G184" s="18" t="b">
         <v>1</v>
       </c>
       <c r="H184" s="17" t="str">
-        <f>_xlfn.TEXTJOIN(", ",,A188,A189)</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-vehicle-fleet-description, https://w3id.org/mobilitydcat-ap/mobility-theme/service-real-time-availability</v>
+        <f>A191</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-locations-and-stations</v>
       </c>
       <c r="I184" s="17" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="185" spans="1:9" s="18" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="15" t="str">
         <f t="shared" si="5"/>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bike-hiring-availability</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/e-scooter-sharing-locations-and-stations</v>
       </c>
       <c r="B185" s="16" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C185" s="16"/>
       <c r="D185" s="17"/>
       <c r="E185" s="17"/>
       <c r="F185" s="17" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="G185" s="18" t="b">
         <v>1</v>
       </c>
       <c r="H185" s="17" t="str">
-        <f>_xlfn.TEXTJOIN(", ",,A188,A189)</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-vehicle-fleet-description, https://w3id.org/mobilitydcat-ap/mobility-theme/service-real-time-availability</v>
+        <f>A191</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-locations-and-stations</v>
       </c>
       <c r="I185" s="17" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="186" spans="1:9" s="18" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" s="18" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="15" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B186,"/","-"))," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/e-scooter-sharing-availability</v>
+        <f t="shared" si="5"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/car-sharing-availability</v>
       </c>
       <c r="B186" s="16" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C186" s="16"/>
       <c r="D186" s="17"/>
       <c r="E186" s="17"/>
       <c r="F186" s="17" t="str">
-        <f>A21</f>
+        <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="G186" s="18" t="b">
         <v>1</v>
       </c>
       <c r="H186" s="17" t="str">
-        <f>_xlfn.TEXTJOIN(", ",,A188,A189)</f>
+        <f>_xlfn.TEXTJOIN(", ",,A192,A193)</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-vehicle-fleet-description, https://w3id.org/mobilitydcat-ap/mobility-theme/service-real-time-availability</v>
       </c>
       <c r="I186" s="17" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="187" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="20" t="str">
+    <row r="187" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A187" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bike-sharing-availability</v>
+      </c>
+      <c r="B187" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="C187" s="16"/>
+      <c r="D187" s="17"/>
+      <c r="E187" s="17"/>
+      <c r="F187" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G187" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H187" s="17" t="str">
+        <f>_xlfn.TEXTJOIN(", ",,A192,A193)</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-vehicle-fleet-description, https://w3id.org/mobilitydcat-ap/mobility-theme/service-real-time-availability</v>
+      </c>
+      <c r="I187" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A188" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/car-hiring-availability</v>
+      </c>
+      <c r="B188" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="C188" s="16"/>
+      <c r="D188" s="17"/>
+      <c r="E188" s="17"/>
+      <c r="F188" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G188" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H188" s="17" t="str">
+        <f>_xlfn.TEXTJOIN(", ",,A192,A193)</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-vehicle-fleet-description, https://w3id.org/mobilitydcat-ap/mobility-theme/service-real-time-availability</v>
+      </c>
+      <c r="I188" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A189" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bike-hiring-availability</v>
+      </c>
+      <c r="B189" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="C189" s="16"/>
+      <c r="D189" s="17"/>
+      <c r="E189" s="17"/>
+      <c r="F189" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G189" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H189" s="17" t="str">
+        <f>_xlfn.TEXTJOIN(", ",,A192,A193)</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-vehicle-fleet-description, https://w3id.org/mobilitydcat-ap/mobility-theme/service-real-time-availability</v>
+      </c>
+      <c r="I189" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A190" s="15" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B190,"/","-"))," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/e-scooter-sharing-availability</v>
+      </c>
+      <c r="B190" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="C190" s="16"/>
+      <c r="D190" s="17"/>
+      <c r="E190" s="17"/>
+      <c r="F190" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G190" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H190" s="17" t="str">
+        <f>_xlfn.TEXTJOIN(", ",,A192,A193)</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-vehicle-fleet-description, https://w3id.org/mobilitydcat-ap/mobility-theme/service-real-time-availability</v>
+      </c>
+      <c r="I190" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="20" t="str">
         <f t="shared" si="5"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-locations-and-stations</v>
       </c>
-      <c r="B187" s="33" t="s">
+      <c r="B191" s="33" t="s">
         <v>228</v>
       </c>
-      <c r="C187" s="24"/>
-      <c r="D187" s="22"/>
-      <c r="E187" s="22"/>
-      <c r="F187" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H187" s="22"/>
-      <c r="I187" s="22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A188" s="20" t="str">
+      <c r="C191" s="24"/>
+      <c r="D191" s="22"/>
+      <c r="E191" s="22"/>
+      <c r="F191" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H191" s="22"/>
+      <c r="I191" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A192" s="20" t="str">
         <f t="shared" si="5"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-vehicle-fleet-description</v>
       </c>
-      <c r="B188" s="24" t="s">
+      <c r="B192" s="24" t="s">
         <v>229</v>
       </c>
-      <c r="C188" s="24"/>
-      <c r="D188" s="22" t="s">
+      <c r="C192" s="24"/>
+      <c r="D192" s="22" t="s">
         <v>230</v>
       </c>
-      <c r="E188" s="22"/>
-      <c r="F188" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H188" s="22"/>
-      <c r="I188" s="22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="189" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="20" t="str">
+      <c r="E192" s="22"/>
+      <c r="F192" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H192" s="22"/>
+      <c r="I192" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="20" t="str">
         <f t="shared" si="5"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-real-time-availability</v>
       </c>
-      <c r="B189" s="24" t="s">
+      <c r="B193" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="C189" s="24"/>
-      <c r="D189" s="22"/>
-      <c r="E189" s="22"/>
-      <c r="F189" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H189" s="22"/>
-      <c r="I189" s="22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="190" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="20" t="str">
+      <c r="C193" s="24"/>
+      <c r="D193" s="22"/>
+      <c r="E193" s="22"/>
+      <c r="F193" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H193" s="22"/>
+      <c r="I193" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="20" t="str">
         <f t="shared" si="5"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-payment-methods</v>
       </c>
-      <c r="B190" s="24" t="s">
+      <c r="B194" s="24" t="s">
         <v>232</v>
       </c>
-      <c r="C190" s="24"/>
-      <c r="D190" s="22"/>
-      <c r="E190" s="22"/>
-      <c r="F190" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H190" s="22"/>
-      <c r="I190" s="22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A191" s="20" t="str">
+      <c r="C194" s="24"/>
+      <c r="D194" s="22"/>
+      <c r="E194" s="22"/>
+      <c r="F194" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H194" s="22"/>
+      <c r="I194" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A195" s="20" t="str">
         <f t="shared" si="5"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-zones</v>
       </c>
-      <c r="B191" s="21" t="s">
+      <c r="B195" s="21" t="s">
         <v>233</v>
       </c>
-      <c r="C191" s="24"/>
-      <c r="D191" s="22" t="s">
+      <c r="C195" s="24"/>
+      <c r="D195" s="22" t="s">
         <v>234</v>
       </c>
-      <c r="E191" s="22"/>
-      <c r="F191" s="22" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="H191" s="22"/>
-      <c r="I191" s="22" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="192" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="15" t="str">
+      <c r="E195" s="22"/>
+      <c r="F195" s="22" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="H195" s="22"/>
+      <c r="I195" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="15" t="str">
         <f t="shared" si="5"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/payment-methods</v>
       </c>
-      <c r="B192" s="16" t="s">
+      <c r="B196" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="C192" s="16"/>
-      <c r="D192" s="17"/>
-      <c r="E192" s="17"/>
-      <c r="F192" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G192" s="18" t="b">
+      <c r="C196" s="16"/>
+      <c r="D196" s="17"/>
+      <c r="E196" s="17"/>
+      <c r="F196" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G196" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="H192" s="17" t="str">
-        <f>A190</f>
+      <c r="H196" s="17" t="str">
+        <f>A194</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-payment-methods</v>
       </c>
-      <c r="I192" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A193" s="15" t="str">
+      <c r="I196" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="15" t="str">
         <f t="shared" si="5"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/environmental-standards-for-vehicles</v>
       </c>
-      <c r="B193" s="16" t="s">
+      <c r="B197" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="C193" s="16"/>
-      <c r="D193" s="17"/>
-      <c r="E193" s="17"/>
-      <c r="F193" s="17" t="str">
-        <f>A21</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
-      </c>
-      <c r="G193" s="18" t="b">
+      <c r="C197" s="16"/>
+      <c r="D197" s="17"/>
+      <c r="E197" s="17"/>
+      <c r="F197" s="17" t="str">
+        <f>A25</f>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
+      </c>
+      <c r="G197" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="H193" s="17" t="str">
-        <f>A188</f>
+      <c r="H197" s="17" t="str">
+        <f>A192</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-vehicle-fleet-description</v>
       </c>
-      <c r="I193" s="17"/>
-    </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A194" s="10" t="str">
+      <c r="I197" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A198" s="10" t="str">
         <f t="shared" si="5"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/air-and-space-travel</v>
       </c>
-      <c r="B194" s="9" t="s">
+      <c r="B198" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="C194" s="8"/>
-      <c r="F194" s="1" t="str">
-        <f>A20</f>
+      <c r="C198" s="8"/>
+      <c r="F198" s="1" t="str">
+        <f>A24</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
-      <c r="I194" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A195" s="10" t="str">
+      <c r="I198" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A199" s="10" t="str">
         <f t="shared" si="5"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/waterways-and-water-bodies</v>
       </c>
-      <c r="B195" s="9" t="s">
+      <c r="B199" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="C195" s="8"/>
-      <c r="F195" s="1" t="str">
-        <f>A20</f>
+      <c r="C199" s="8"/>
+      <c r="F199" s="1" t="str">
+        <f>A24</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
-      <c r="I195" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A196" s="10" t="str">
+      <c r="I199" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A200" s="10" t="str">
         <f t="shared" si="5"/>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/other</v>
       </c>
-      <c r="B196" s="9" t="s">
+      <c r="B200" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="C196" s="8"/>
-      <c r="F196" s="1" t="str">
-        <f>A20</f>
+      <c r="C200" s="8"/>
+      <c r="F200" s="1" t="str">
+        <f>A24</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A19:I195" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A23:I200" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B1" r:id="rId1" display="https://w3id.org/mobilitydcat-ap/data-content-category" xr:uid="{8D37ED2A-6F4C-4B2C-B212-84B5255111B4}"/>
-    <hyperlink ref="B14" r:id="rId2" xr:uid="{F5CCEF78-A2AE-420B-8B79-2E74A78B421A}"/>
-    <hyperlink ref="I19" r:id="rId3" xr:uid="{F154D901-F5CC-4BA5-8C60-65E6B8A7F74B}"/>
+    <hyperlink ref="B18" r:id="rId2" xr:uid="{F5CCEF78-A2AE-420B-8B79-2E74A78B421A}"/>
+    <hyperlink ref="I23" r:id="rId3" xr:uid="{F154D901-F5CC-4BA5-8C60-65E6B8A7F74B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId4"/>
@@ -5374,6 +5453,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006748505E66128D48AAED90CD5CD3616F" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b912ec8155dd4e933917767331a7e7b9">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa" xmlns:ns3="13e36eaf-61a1-47aa-b343-0f7d626aa9a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f994fb40b965d01e7e08c4f92ceb61cd" ns2:_="" ns3:_="">
     <xsd:import namespace="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa"/>
@@ -5574,15 +5662,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -5595,6 +5674,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{354E852E-38F4-443F-ABCC-E4BE2043727A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4E03DED-ABA6-41DC-A9F2-F03B3D97B70D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5613,14 +5700,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{354E852E-38F4-443F-ABCC-E4BE2043727A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F704F36C-6F34-42D8-A9E1-097741891E9D}">
   <ds:schemaRefs>

--- a/mobility-theme/mobility-theme.xlsx
+++ b/mobility-theme/mobility-theme.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scrocca\Desktop\cefriel-github\controlled-vocabularies\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B6A31C-5EDA-47E2-8551-22E6838A6B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{765DA844-301F-4959-A8DD-12A3D7C4C34D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vocabulary" sheetId="2" r:id="rId1"/>
@@ -19,8 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Vocabulary!$A$23:$I$200</definedName>
   </definedNames>
-  <calcPr calcId="191028" iterateDelta="1E-4"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -59,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="261">
   <si>
     <t>ConceptScheme URI</t>
   </si>
@@ -85,9 +84,6 @@
     <t>dct:publisher</t>
   </si>
   <si>
-    <t>NAPCORE WG4 Task 4.4</t>
-  </si>
-  <si>
     <t>dct:contributor</t>
   </si>
   <si>
@@ -148,9 +144,6 @@
     <t>owl:deprecated^^xsd:boolean</t>
   </si>
   <si>
-    <t>dcterms:replacedBy</t>
-  </si>
-  <si>
     <t>http://data.europa.eu/r5r/applicableLegislation</t>
   </si>
   <si>
@@ -388,21 +381,9 @@
     <t>Availability of filling stations</t>
   </si>
   <si>
-    <t>https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-characteristics-filling-charging-stations</t>
-  </si>
-  <si>
-    <t>Location and characteristics for filling stations and charging stations</t>
-  </si>
-  <si>
-    <t>https://w3id.org/mobilitydcat-ap/mobility-theme/availability-filling-charging-stations</t>
-  </si>
-  <si>
     <t>Availability of filling stations and charging stations</t>
   </si>
   <si>
-    <t>https://w3id.org/mobilitydcat-ap/mobility-theme/prices-of-filling-charging-stations</t>
-  </si>
-  <si>
     <t>Prices of filling stations and charging stations</t>
   </si>
   <si>
@@ -553,9 +534,6 @@
     <t>Public transport scheduled transport</t>
   </si>
   <si>
-    <t>https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-on-demand-services</t>
-  </si>
-  <si>
     <t>Public transport and on-demand services</t>
   </si>
   <si>
@@ -670,9 +648,6 @@
     <t>Observed data on cancellations</t>
   </si>
   <si>
-    <t>https://w3id.org/mobilitydcat-ap/mobility-theme/vehicle-occupancy</t>
-  </si>
-  <si>
     <t>Vehicle occupancy</t>
   </si>
   <si>
@@ -841,9 +816,6 @@
     <t>Commission Delegated Regulation (EU) 2024/490 of 29 November 2023 amending Delegated Regulation (EU) 2017/1926 supplementing Directive 2010/40/EU of the European Parliament and of the Council with regard to the provision of EU-wide multimodal travel information services</t>
   </si>
   <si>
-    <t>Draft Controlled Vocabulary</t>
-  </si>
-  <si>
     <t>Mobility Theme</t>
   </si>
   <si>
@@ -857,6 +829,18 @@
   </si>
   <si>
     <t>Christian Rantzow von Huth (Vejdirektoratet)</t>
+  </si>
+  <si>
+    <t>dcterms:isReplacedBy</t>
+  </si>
+  <si>
+    <t>NAPCORE Task 4.4</t>
+  </si>
+  <si>
+    <t>Published Controlled Vocabulary</t>
+  </si>
+  <si>
+    <t>Location and characteristics of filling stations and charging stations</t>
   </si>
 </sst>
 </file>
@@ -1409,7 +1393,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1441,7 +1425,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1449,77 +1433,77 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="14" t="s">
         <v>14</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>15</v>
       </c>
       <c r="C15" s="14"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" t="str">
         <f>_xlfn.CONCAT(B1,"/",B15)</f>
@@ -1528,56 +1512,56 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
         <v>17</v>
-      </c>
-      <c r="B17" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="C18" s="6"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="F23" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="H23" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1586,7 +1570,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="29"/>
@@ -1600,7 +1584,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="29"/>
@@ -1617,7 +1601,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/static-road-network-data</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C26" s="8"/>
       <c r="E26" s="25" t="str">
@@ -1629,7 +1613,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
       <c r="I26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -1638,7 +1622,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/geometry</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C27" s="19"/>
       <c r="D27" s="17"/>
@@ -1655,7 +1639,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-network-geometry</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -1664,7 +1648,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-network-geometry</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C28" s="21"/>
       <c r="D28" s="22"/>
@@ -1675,7 +1659,7 @@
       </c>
       <c r="H28" s="22"/>
       <c r="I28" s="22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -1684,7 +1668,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-width</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C29" s="7"/>
       <c r="F29" s="1" t="str">
@@ -1692,7 +1676,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -1701,7 +1685,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/number-of-lanes</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C30" s="19"/>
       <c r="D30" s="17"/>
@@ -1718,7 +1702,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-number-of-lanes</v>
       </c>
       <c r="I30" s="17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -1727,7 +1711,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-number-of-lanes</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C31" s="21"/>
       <c r="D31" s="22"/>
@@ -1738,7 +1722,7 @@
       </c>
       <c r="H31" s="22"/>
       <c r="I31" s="22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -1747,7 +1731,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/gradients</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C32" s="19"/>
       <c r="D32" s="17"/>
@@ -1764,7 +1748,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-gradients</v>
       </c>
       <c r="I32" s="17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -1773,7 +1757,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-gradients</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C33" s="21"/>
       <c r="D33" s="22"/>
@@ -1784,7 +1768,7 @@
       </c>
       <c r="H33" s="22"/>
       <c r="I33" s="22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -1793,7 +1777,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/junctions</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C34" s="19"/>
       <c r="D34" s="17"/>
@@ -1810,7 +1794,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-junctions</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -1819,7 +1803,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-junctions</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C35" s="21"/>
       <c r="D35" s="22"/>
@@ -1830,7 +1814,7 @@
       </c>
       <c r="H35" s="22"/>
       <c r="I35" s="22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -1839,7 +1823,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-classification</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C36" s="7"/>
       <c r="F36" s="1" t="str">
@@ -1847,7 +1831,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="90" x14ac:dyDescent="0.25">
@@ -1856,7 +1840,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/cycle-network-data</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C37" s="8"/>
       <c r="E37" s="25" t="str">
@@ -1868,7 +1852,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -1877,7 +1861,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/network-geometry-and-lane-character</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C38" s="16"/>
       <c r="D38" s="17"/>
@@ -1890,10 +1874,10 @@
         <v>1</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I38" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -1902,11 +1886,11 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/cycle-network-geometry</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C39" s="24"/>
       <c r="D39" s="22" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E39" s="22"/>
       <c r="F39" s="22" t="str">
@@ -1915,7 +1899,7 @@
       </c>
       <c r="H39" s="22"/>
       <c r="I39" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -1924,7 +1908,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/network-detailed-attributes</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C40" s="16"/>
       <c r="D40" s="17"/>
@@ -1937,10 +1921,10 @@
         <v>1</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I40" s="18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -1949,7 +1933,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/cycle-network-detailed-attributes</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C41" s="24"/>
       <c r="D41" s="22"/>
@@ -1960,7 +1944,7 @@
       </c>
       <c r="H41" s="22"/>
       <c r="I41" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -1969,7 +1953,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/network-closures-diversions</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C42" s="16"/>
       <c r="D42" s="17"/>
@@ -1982,10 +1966,10 @@
         <v>1</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I42" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -1994,7 +1978,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/cycle-network-closures-diversions</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C43" s="24"/>
       <c r="D43" s="22"/>
@@ -2005,7 +1989,7 @@
       </c>
       <c r="H43" s="22"/>
       <c r="I43" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -2014,7 +1998,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/pedestrian-network-data</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C44" s="8"/>
       <c r="E44" s="1" t="str">
@@ -2026,7 +2010,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -2035,7 +2019,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/pedestrian-network-geometry</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C45" s="8"/>
       <c r="F45" s="1" t="str">
@@ -2043,7 +2027,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -2052,7 +2036,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/pedestrian-accessibility-facilities</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C46" s="8"/>
       <c r="F46" s="1" t="str">
@@ -2060,7 +2044,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2069,7 +2053,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/static-traffic-signs-and-regulations</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C47" s="8"/>
       <c r="E47" s="25" t="str">
@@ -2081,7 +2065,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -2090,7 +2074,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/tunnel-access-conditions</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C48" s="8"/>
       <c r="F48" s="1" t="str">
@@ -2098,7 +2082,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -2107,7 +2091,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bridge-access-conditions</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C49" s="8"/>
       <c r="F49" s="1" t="str">
@@ -2115,7 +2099,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -2124,7 +2108,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/speed-limits</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C50" s="8"/>
       <c r="F50" s="1" t="str">
@@ -2132,7 +2116,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
@@ -2141,7 +2125,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/other-static-traffic-signs</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C51" s="8"/>
       <c r="F51" s="1" t="str">
@@ -2149,7 +2133,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I51" s="25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
@@ -2158,7 +2142,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/permanent-access-restrictions</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C52" s="8"/>
       <c r="F52" s="1" t="str">
@@ -2166,7 +2150,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
@@ -2175,7 +2159,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/other-traffic-regulations</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C53" s="8"/>
       <c r="F53" s="1" t="str">
@@ -2183,7 +2167,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -2192,7 +2176,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/traffic-circulation-plans</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C54" s="8"/>
       <c r="F54" s="1" t="str">
@@ -2200,7 +2184,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -2209,7 +2193,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/static-overtaking-bans-on-heavy-goods-vehicles</v>
       </c>
       <c r="B55" s="24" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C55" s="8"/>
       <c r="D55" s="22"/>
@@ -2220,7 +2204,7 @@
       </c>
       <c r="H55" s="22"/>
       <c r="I55" s="22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -2229,7 +2213,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/weight-length-width-height-restrictions</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C56" s="8"/>
       <c r="D56" s="22"/>
@@ -2240,7 +2224,7 @@
       </c>
       <c r="H56" s="22"/>
       <c r="I56" s="22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="57" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -2249,7 +2233,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/one-way-streets</v>
       </c>
       <c r="B57" s="24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="22"/>
@@ -2260,7 +2244,7 @@
       </c>
       <c r="H57" s="22"/>
       <c r="I57" s="22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58" spans="1:9" s="23" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -2269,11 +2253,11 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/regulated-traffic-zones</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C58" s="8"/>
       <c r="D58" s="22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E58" s="22"/>
       <c r="F58" s="22" t="str">
@@ -2282,7 +2266,7 @@
       </c>
       <c r="H58" s="22"/>
       <c r="I58" s="22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="90" x14ac:dyDescent="0.25">
@@ -2291,7 +2275,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/toll-information</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C59" s="8"/>
       <c r="E59" s="25" t="str">
@@ -2303,7 +2287,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
@@ -2312,7 +2296,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-of-tolling-stations</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C60" s="8"/>
       <c r="F60" s="1" t="str">
@@ -2320,7 +2304,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
@@ -2329,7 +2313,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/identification-of-tolled-roads</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C61" s="8"/>
       <c r="F61" s="1" t="str">
@@ -2337,7 +2321,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62" spans="1:9" s="18" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -2346,7 +2330,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/applicable-road-user-charges-and-payment-methods</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C62" s="16"/>
       <c r="D62" s="17"/>
@@ -2363,7 +2347,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/fixed-road-user-charges-and-payment-methods</v>
       </c>
       <c r="I62" s="18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -2372,7 +2356,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/fixed-road-user-charges-and-payment-methods</v>
       </c>
       <c r="B63" s="24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C63" s="24"/>
       <c r="D63" s="22"/>
@@ -2383,7 +2367,7 @@
       </c>
       <c r="H63" s="22"/>
       <c r="I63" s="23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="64" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -2392,7 +2376,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/variable-road-user-charges-and-payment-methods</v>
       </c>
       <c r="B64" s="24" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C64" s="24"/>
       <c r="D64" s="22"/>
@@ -2403,7 +2387,7 @@
       </c>
       <c r="H64" s="22"/>
       <c r="I64" s="23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:9" s="18" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2412,7 +2396,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/payment-methods-for-tolls</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C65" s="16"/>
       <c r="D65" s="17"/>
@@ -2429,7 +2413,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/fixed-road-user-charges-and-payment-methods,https://w3id.org/mobilitydcat-ap/mobility-theme/variable-road-user-charges-and-payment-methods</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="144" customHeight="1" x14ac:dyDescent="0.25">
@@ -2438,7 +2422,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-service-and-rest-area-information</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C66" s="8"/>
       <c r="E66" s="25" t="str">
@@ -2450,7 +2434,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="67" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -2459,7 +2443,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/car-parking-locations-and-conditions</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C67" s="16"/>
       <c r="D67" s="17"/>
@@ -2476,7 +2460,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-locations-description-and-facilities</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -2485,7 +2469,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/car-parking-availability</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C68" s="16"/>
       <c r="D68" s="17"/>
@@ -2502,7 +2486,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-real-time-availability</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="69" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -2511,7 +2495,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-locations-description-and-facilities</v>
       </c>
       <c r="B69" s="24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C69" s="24"/>
       <c r="D69" s="22"/>
@@ -2522,7 +2506,7 @@
       </c>
       <c r="H69" s="22"/>
       <c r="I69" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -2531,7 +2515,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-zones</v>
       </c>
       <c r="B70" s="24" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C70" s="24"/>
       <c r="D70" s="22"/>
@@ -2542,7 +2526,7 @@
       </c>
       <c r="H70" s="22"/>
       <c r="I70" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -2551,7 +2535,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-real-time-availability</v>
       </c>
       <c r="B71" s="24" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C71" s="24"/>
       <c r="D71" s="22"/>
@@ -2562,7 +2546,7 @@
       </c>
       <c r="H71" s="22"/>
       <c r="I71" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="72" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -2571,7 +2555,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-conditions-and-tariffs</v>
       </c>
       <c r="B72" s="24" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C72" s="24"/>
       <c r="D72" s="22"/>
@@ -2582,7 +2566,7 @@
       </c>
       <c r="H72" s="22"/>
       <c r="I72" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="73" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -2591,11 +2575,11 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-payment-points-and-methods</v>
       </c>
       <c r="B73" s="24" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C73" s="24"/>
       <c r="D73" s="22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E73" s="22"/>
       <c r="F73" s="22" t="str">
@@ -2604,7 +2588,7 @@
       </c>
       <c r="H73" s="22"/>
       <c r="I73" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -2613,7 +2597,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-and-rest-area-locations-and-conditions</v>
       </c>
       <c r="B74" s="16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C74" s="16"/>
       <c r="D74" s="17"/>
@@ -2630,7 +2614,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-and-rest-area-locations-description-and-facilities</v>
       </c>
       <c r="I74" s="17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="75" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -2639,7 +2623,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-and-rest-area-locations-description-and-facilities</v>
       </c>
       <c r="B75" s="24" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C75" s="24"/>
       <c r="D75" s="22"/>
@@ -2650,7 +2634,7 @@
       </c>
       <c r="H75" s="22"/>
       <c r="I75" s="23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="76" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -2659,7 +2643,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-and-rest-area-availability</v>
       </c>
       <c r="B76" s="16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C76" s="16"/>
       <c r="D76" s="17"/>
@@ -2676,7 +2660,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-and-rest-area-real-time-availability</v>
       </c>
       <c r="I76" s="18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -2685,7 +2669,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-and-rest-area-real-time-availability</v>
       </c>
       <c r="B77" s="24" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C77" s="24"/>
       <c r="D77" s="22"/>
@@ -2696,7 +2680,7 @@
       </c>
       <c r="H77" s="22"/>
       <c r="I77" s="23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -2705,7 +2689,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/truck-parking-locations-and-conditions</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C78" s="16"/>
       <c r="D78" s="17"/>
@@ -2722,7 +2706,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-locations-description-and-facilities</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="79" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -2731,7 +2715,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/truck-parking-availability</v>
       </c>
       <c r="B79" s="16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C79" s="16"/>
       <c r="D79" s="17"/>
@@ -2748,7 +2732,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-real-time-availability</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -2757,18 +2741,18 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/park-and-ride-stops</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C80" s="8"/>
       <c r="D80" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F80" s="1" t="str">
         <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="81" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -2777,11 +2761,11 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/park-and-drive-stops</v>
       </c>
       <c r="B81" s="24" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C81" s="24"/>
       <c r="D81" s="22" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E81" s="22"/>
       <c r="F81" s="22" t="str">
@@ -2790,7 +2774,7 @@
       </c>
       <c r="H81" s="22"/>
       <c r="I81" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="82" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -2799,7 +2783,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/kiss-and-ride-stops</v>
       </c>
       <c r="B82" s="24" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C82" s="24"/>
       <c r="D82" s="22"/>
@@ -2810,7 +2794,7 @@
       </c>
       <c r="H82" s="22"/>
       <c r="I82" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="83" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -2819,7 +2803,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bike-parking-locations</v>
       </c>
       <c r="B83" s="16" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C83" s="16"/>
       <c r="D83" s="17"/>
@@ -2836,7 +2820,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parking-locations-description-and-facilities</v>
       </c>
       <c r="I83" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -2845,19 +2829,19 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/filling-and-charging-stations</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C84" s="8"/>
       <c r="E84" s="25" t="str">
         <f>_xlfn.TEXTJOIN(", ",,A89:A91)</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-characteristics-filling-charging-stations, https://w3id.org/mobilitydcat-ap/mobility-theme/availability-filling-charging-stations, https://w3id.org/mobilitydcat-ap/mobility-theme/prices-of-filling-charging-stations</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-characteristics-of-filling-stations-and-charging-stations, https://w3id.org/mobilitydcat-ap/mobility-theme/availability-of-filling-stations-and-charging-stations, https://w3id.org/mobilitydcat-ap/mobility-theme/prices-of-filling-stations-and-charging-stations</v>
       </c>
       <c r="F84" s="1" t="str">
         <f>A24</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
       <c r="I84" s="25" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="85" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -2866,7 +2850,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-conditions-of-charging-points</v>
       </c>
       <c r="B85" s="16" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C85" s="16"/>
       <c r="D85" s="17"/>
@@ -2880,10 +2864,10 @@
       </c>
       <c r="H85" s="17" t="str">
         <f>A89</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-characteristics-filling-charging-stations</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-characteristics-of-filling-stations-and-charging-stations</v>
       </c>
       <c r="I85" s="17" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="86" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -2892,7 +2876,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-conditions-of-filling-stations</v>
       </c>
       <c r="B86" s="16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C86" s="16"/>
       <c r="D86" s="17"/>
@@ -2906,10 +2890,10 @@
       </c>
       <c r="H86" s="17" t="str">
         <f>A89</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-characteristics-filling-charging-stations</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-characteristics-of-filling-stations-and-charging-stations</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -2918,7 +2902,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/availability-of-charging-points-for-electric-vehicles</v>
       </c>
       <c r="B87" s="16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C87" s="16"/>
       <c r="D87" s="17"/>
@@ -2932,10 +2916,10 @@
       </c>
       <c r="H87" s="17" t="str">
         <f>A90</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/availability-filling-charging-stations</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/availability-of-filling-stations-and-charging-stations</v>
       </c>
       <c r="I87" s="17" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="88" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -2944,7 +2928,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/availability-of-filling-stations</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C88" s="16"/>
       <c r="D88" s="17"/>
@@ -2958,18 +2942,19 @@
       </c>
       <c r="H88" s="17" t="str">
         <f>A90</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/availability-filling-charging-stations</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/availability-of-filling-stations-and-charging-stations</v>
       </c>
       <c r="I88" s="17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="89" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A89" s="20" t="s">
-        <v>109</v>
+      <c r="A89" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-characteristics-of-filling-stations-and-charging-stations</v>
       </c>
       <c r="B89" s="24" t="s">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="C89" s="24"/>
       <c r="D89" s="22"/>
@@ -2980,15 +2965,16 @@
       </c>
       <c r="H89" s="22"/>
       <c r="I89" s="22" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="90" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A90" s="20" t="s">
-        <v>111</v>
+      <c r="A90" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/availability-of-filling-stations-and-charging-stations</v>
       </c>
       <c r="B90" s="24" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C90" s="24"/>
       <c r="D90" s="22"/>
@@ -2999,15 +2985,16 @@
       </c>
       <c r="H90" s="22"/>
       <c r="I90" s="22" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="91" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A91" s="20" t="s">
-        <v>113</v>
+      <c r="A91" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/prices-of-filling-stations-and-charging-stations</v>
       </c>
       <c r="B91" s="24" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C91" s="24"/>
       <c r="D91" s="22"/>
@@ -3018,7 +3005,7 @@
       </c>
       <c r="H91" s="22"/>
       <c r="I91" s="22" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -3027,7 +3014,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/freight-and-logistics</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C92" s="8"/>
       <c r="E92" s="1" t="str">
@@ -3039,7 +3026,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
@@ -3048,7 +3035,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/freight-delivery-regulations</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C93" s="8"/>
       <c r="F93" s="1" t="str">
@@ -3056,7 +3043,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
@@ -3065,7 +3052,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-of-delivery-areas</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C94" s="8"/>
       <c r="F94" s="1" t="str">
@@ -3073,7 +3060,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
@@ -3082,7 +3069,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/availability-of-delivery-areas</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C95" s="8"/>
       <c r="F95" s="1" t="str">
@@ -3090,7 +3077,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="150" x14ac:dyDescent="0.25">
@@ -3099,7 +3086,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/dynamic-traffic-signs-and-regulations</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C96" s="8"/>
       <c r="E96" s="1" t="str">
@@ -3111,7 +3098,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
@@ -3120,7 +3107,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-closures-and-access-conditions</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C97" s="8"/>
       <c r="F97" s="1" t="str">
@@ -3128,7 +3115,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
@@ -3137,7 +3124,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/lane-closures-and-access-conditions</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C98" s="8"/>
       <c r="F98" s="1" t="str">
@@ -3145,7 +3132,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
@@ -3154,7 +3141,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bridge-closures-and-access-conditions</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C99" s="8"/>
       <c r="F99" s="1" t="str">
@@ -3162,7 +3149,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
@@ -3171,7 +3158,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/tunnel-closures-and-access-conditions</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C100" s="8"/>
       <c r="F100" s="1" t="str">
@@ -3179,7 +3166,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
@@ -3188,7 +3175,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/other-access-restrictions-and-traffic-regulations</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C101" s="8"/>
       <c r="F101" s="1" t="str">
@@ -3196,7 +3183,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
@@ -3205,7 +3192,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/dynamic-overtaking-bans-on-heavy-goods-vehicles</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C102" s="8"/>
       <c r="F102" s="1" t="str">
@@ -3213,7 +3200,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
@@ -3222,7 +3209,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/dynamic-speed-limits</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C103" s="8"/>
       <c r="F103" s="1" t="str">
@@ -3230,7 +3217,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
@@ -3239,7 +3226,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/direction-of-travel-on-reversible-lanes</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C104" s="8"/>
       <c r="F104" s="1" t="str">
@@ -3247,7 +3234,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
@@ -3256,7 +3243,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/other-temporary-traffic-management-measures-or-plans</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C105" s="8"/>
       <c r="F105" s="1" t="str">
@@ -3264,7 +3251,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -3273,7 +3260,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-work-information</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C106" s="8"/>
       <c r="E106" s="1" t="str">
@@ -3285,7 +3272,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
@@ -3294,7 +3281,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/long-term-road-works</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C107" s="8"/>
       <c r="F107" s="1" t="str">
@@ -3302,7 +3289,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -3311,7 +3298,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/short-term-road-works</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C108" s="8"/>
       <c r="F108" s="1" t="str">
@@ -3319,7 +3306,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -3328,7 +3315,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-events-and-conditions</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C109" s="8"/>
       <c r="E109" s="1" t="str">
@@ -3340,7 +3327,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -3349,7 +3336,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/accidents-and-incidents</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C110" s="8"/>
       <c r="F110" s="1" t="str">
@@ -3357,7 +3344,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -3366,7 +3353,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/poor-road-conditions</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C111" s="8"/>
       <c r="F111" s="1" t="str">
@@ -3374,7 +3361,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -3383,7 +3370,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/road-weather-conditions</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C112" s="8"/>
       <c r="F112" s="1" t="str">
@@ -3391,7 +3378,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="165" x14ac:dyDescent="0.25">
@@ -3400,7 +3387,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/real-time-traffic-data</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C113" s="8"/>
       <c r="E113" s="25" t="str">
@@ -3412,7 +3399,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
@@ -3421,7 +3408,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/traffic-volume</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C114" s="8"/>
       <c r="F114" s="1" t="str">
@@ -3429,7 +3416,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="115" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -3438,7 +3425,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/speed</v>
       </c>
       <c r="B115" s="16" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C115" s="16"/>
       <c r="D115" s="17"/>
@@ -3451,10 +3438,10 @@
         <v>1</v>
       </c>
       <c r="H115" s="18" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="I115" s="17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="116" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -3463,7 +3450,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/traffic-speed</v>
       </c>
       <c r="B116" s="24" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C116" s="24"/>
       <c r="D116" s="22"/>
@@ -3474,7 +3461,7 @@
       </c>
       <c r="H116" s="22"/>
       <c r="I116" s="22" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
@@ -3483,7 +3470,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/location-and-length-of-traffic-queues</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C117" s="8"/>
       <c r="F117" s="1" t="str">
@@ -3491,7 +3478,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="118" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -3500,7 +3487,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/current-travel-times</v>
       </c>
       <c r="B118" s="16" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C118" s="16"/>
       <c r="D118" s="17"/>
@@ -3517,7 +3504,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/current-road-travel-times</v>
       </c>
       <c r="I118" s="18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="119" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -3526,7 +3513,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/current-road-travel-times</v>
       </c>
       <c r="B119" s="24" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C119" s="24"/>
       <c r="D119" s="22"/>
@@ -3537,7 +3524,7 @@
       </c>
       <c r="H119" s="22"/>
       <c r="I119" s="23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="120" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -3546,7 +3533,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/predicted-travel-times</v>
       </c>
       <c r="B120" s="16" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C120" s="16"/>
       <c r="D120" s="17"/>
@@ -3563,7 +3550,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/predicted-road-travel-times</v>
       </c>
       <c r="I120" s="17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="121" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -3572,7 +3559,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/predicted-road-travel-times</v>
       </c>
       <c r="B121" s="24" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C121" s="24"/>
       <c r="D121" s="22"/>
@@ -3583,7 +3570,7 @@
       </c>
       <c r="H121" s="22"/>
       <c r="I121" s="23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="122" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -3592,7 +3579,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/expected-delays</v>
       </c>
       <c r="B122" s="16" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C122" s="16"/>
       <c r="D122" s="17"/>
@@ -3609,7 +3596,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/expected-road-traffic-delays</v>
       </c>
       <c r="I122" s="17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="123" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -3618,7 +3605,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/expected-road-traffic-delays</v>
       </c>
       <c r="B123" s="24" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C123" s="24"/>
       <c r="D123" s="22"/>
@@ -3629,7 +3616,7 @@
       </c>
       <c r="H123" s="22"/>
       <c r="I123" s="23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
@@ -3638,7 +3625,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/waiting-time-at-border-crossings-to-non-eu-member-states</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C124" s="8"/>
       <c r="F124" s="1" t="str">
@@ -3646,7 +3633,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
@@ -3655,7 +3642,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/traffic-data-at-border-crossings-to-third-countries</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C125" s="8"/>
       <c r="F125" s="1" t="str">
@@ -3663,7 +3650,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I125" s="25" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3672,7 +3659,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/general-information-for-trip-planning</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C126" s="8"/>
       <c r="E126" s="1" t="str">
@@ -3684,7 +3671,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
@@ -3693,7 +3680,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/address-identifiers</v>
       </c>
       <c r="B127" s="8" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C127" s="8"/>
       <c r="F127" s="1" t="str">
@@ -3701,7 +3688,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
@@ -3710,7 +3697,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/topographic-places</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C128" s="8"/>
       <c r="F128" s="1" t="str">
@@ -3718,7 +3705,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
@@ -3727,7 +3714,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/points-of-interest</v>
       </c>
       <c r="B129" s="8" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C129" s="8"/>
       <c r="F129" s="1" t="str">
@@ -3735,7 +3722,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="45" x14ac:dyDescent="0.25">
@@ -3744,18 +3731,18 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parameters-needed-to-calculate-environmental-factors</v>
       </c>
       <c r="B130" s="8" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C130" s="8"/>
       <c r="D130" s="1" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F130" s="1" t="str">
         <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="131" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3764,7 +3751,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parameters-needed-to-calculate-costs</v>
       </c>
       <c r="B131" s="16" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C131" s="16"/>
       <c r="D131" s="17"/>
@@ -3777,10 +3764,10 @@
         <v>1</v>
       </c>
       <c r="H131" s="17" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="I131" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="132" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3789,11 +3776,11 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/parameters-needed-to-calculate-energy-fuel-consumption</v>
       </c>
       <c r="B132" s="24" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C132" s="24"/>
       <c r="D132" s="22" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E132" s="22"/>
       <c r="F132" s="22" t="str">
@@ -3802,7 +3789,7 @@
       </c>
       <c r="H132" s="22"/>
       <c r="I132" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="133" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3811,11 +3798,11 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/estimated-travel-times-for-multimodal-trip-planning</v>
       </c>
       <c r="B133" s="21" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C133" s="24"/>
       <c r="D133" s="22" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E133" s="22"/>
       <c r="F133" s="22" t="str">
@@ -3824,16 +3811,16 @@
       </c>
       <c r="H133" s="22"/>
       <c r="I133" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="134" spans="1:9" s="18" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="15" t="str">
-        <f t="shared" ref="A134" si="4">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B134,"/","-"))," ","-"),",",""))</f>
+        <f t="shared" ref="A134:A135" si="4">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(SUBSTITUTE(B134,"/","-"))," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-scheduled-transport</v>
       </c>
       <c r="B134" s="16" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C134" s="16"/>
       <c r="D134" s="17"/>
@@ -3847,18 +3834,19 @@
       </c>
       <c r="H134" s="17" t="str">
         <f>A135</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-on-demand-services</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-and-on-demand-services</v>
       </c>
       <c r="I134" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="135" spans="1:9" s="23" customFormat="1" ht="359.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>164</v>
+      <c r="A135" s="20" t="str">
+        <f t="shared" si="4"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-and-on-demand-services</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C135" s="24"/>
       <c r="D135" s="22"/>
@@ -3872,7 +3860,7 @@
       </c>
       <c r="H135" s="22"/>
       <c r="I135" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="136" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -3881,7 +3869,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/stop-facilities-location-and-features</v>
       </c>
       <c r="B136" s="16" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C136" s="16"/>
       <c r="D136" s="17"/>
@@ -3898,7 +3886,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-location-and-features</v>
       </c>
       <c r="I136" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="137" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -3907,7 +3895,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-location-and-features</v>
       </c>
       <c r="B137" s="24" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C137" s="24"/>
       <c r="D137" s="22"/>
@@ -3918,7 +3906,7 @@
       </c>
       <c r="H137" s="22"/>
       <c r="I137" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="138" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -3927,7 +3915,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/stop-facilities-geometry-and-map-layout</v>
       </c>
       <c r="B138" s="16" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C138" s="16"/>
       <c r="D138" s="17"/>
@@ -3944,7 +3932,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-geometry-and-map-layout</v>
       </c>
       <c r="I138" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="139" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -3953,7 +3941,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-geometry-and-map-layout</v>
       </c>
       <c r="B139" s="24" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C139" s="24"/>
       <c r="D139" s="22"/>
@@ -3964,7 +3952,7 @@
       </c>
       <c r="H139" s="22"/>
       <c r="I139" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="140" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -3973,7 +3961,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/stop-facilities-status-of-features</v>
       </c>
       <c r="B140" s="16" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C140" s="16"/>
       <c r="D140" s="17"/>
@@ -3990,7 +3978,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-features-status</v>
       </c>
       <c r="I140" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="141" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -3999,7 +3987,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-features-status</v>
       </c>
       <c r="B141" s="24" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="C141" s="24"/>
       <c r="D141" s="22"/>
@@ -4010,7 +3998,7 @@
       </c>
       <c r="H141" s="22"/>
       <c r="I141" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="142" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -4019,7 +4007,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/stop-facilities-accessibility-and-paths-within-facility</v>
       </c>
       <c r="B142" s="16" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C142" s="16"/>
       <c r="D142" s="17"/>
@@ -4036,7 +4024,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/accessibility-and-paths-within-facilities</v>
       </c>
       <c r="I142" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="143" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -4045,7 +4033,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/accessibility-and-paths-within-facilities</v>
       </c>
       <c r="B143" s="24" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C143" s="24"/>
       <c r="D143" s="22"/>
@@ -4056,7 +4044,7 @@
       </c>
       <c r="H143" s="22"/>
       <c r="I143" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
@@ -4065,7 +4053,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/operational-calendar</v>
       </c>
       <c r="B144" s="8" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C144" s="8"/>
       <c r="F144" s="1" t="str">
@@ -4073,7 +4061,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
@@ -4082,7 +4070,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/connection-links</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C145" s="8"/>
       <c r="F145" s="1" t="str">
@@ -4090,7 +4078,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
@@ -4099,7 +4087,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/network-topology-and-routes-lines</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C146" s="8"/>
       <c r="F146" s="1" t="str">
@@ -4107,7 +4095,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
@@ -4116,7 +4104,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/transport-operators</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C147" s="8"/>
       <c r="F147" s="1" t="str">
@@ -4124,7 +4112,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
@@ -4133,7 +4121,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/timetables-static</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C148" s="8"/>
       <c r="F148" s="1" t="str">
@@ -4141,7 +4129,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
@@ -4150,7 +4138,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/real-time-estimated-departure-and-arrival-times</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C149" s="8"/>
       <c r="F149" s="1" t="str">
@@ -4158,7 +4146,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
@@ -4167,7 +4155,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/planned-interchanges-between-scheduled-services</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C150" s="8"/>
       <c r="F150" s="1" t="str">
@@ -4175,7 +4163,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
@@ -4184,18 +4172,18 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/hours-of-operation</v>
       </c>
       <c r="B151" s="8" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C151" s="8"/>
       <c r="D151" s="1" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="F151" s="1" t="str">
         <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="152" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -4204,7 +4192,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/vehicle-details</v>
       </c>
       <c r="B152" s="16" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C152" s="16"/>
       <c r="D152" s="17"/>
@@ -4221,7 +4209,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/transport-operator-vehicle-fleet-description</v>
       </c>
       <c r="I152" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="153" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4230,11 +4218,11 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/transport-operator-vehicle-fleet-description</v>
       </c>
       <c r="B153" s="24" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C153" s="24"/>
       <c r="D153" s="22" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E153" s="22"/>
       <c r="F153" s="22" t="str">
@@ -4243,7 +4231,7 @@
       </c>
       <c r="H153" s="22"/>
       <c r="I153" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="154" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -4252,7 +4240,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/environmental-standards-for-vehicles</v>
       </c>
       <c r="B154" s="16" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C154" s="16"/>
       <c r="D154" s="17"/>
@@ -4269,7 +4257,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/transport-operator-vehicle-fleet-description</v>
       </c>
       <c r="I154" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
@@ -4278,7 +4266,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/disruptions-delays-cancellations</v>
       </c>
       <c r="B155" s="8" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C155" s="8"/>
       <c r="F155" s="1" t="str">
@@ -4286,7 +4274,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
@@ -4295,7 +4283,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/basic-common-standard-fares</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C156" s="8"/>
       <c r="F156" s="1" t="str">
@@ -4303,7 +4291,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
@@ -4312,7 +4300,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/passenger-classes</v>
       </c>
       <c r="B157" s="8" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C157" s="8"/>
       <c r="F157" s="1" t="str">
@@ -4320,7 +4308,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
@@ -4329,7 +4317,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/common-fare-products</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C158" s="8"/>
       <c r="F158" s="1" t="str">
@@ -4337,7 +4325,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
@@ -4346,7 +4334,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/special-fare-products</v>
       </c>
       <c r="B159" s="8" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C159" s="8"/>
       <c r="F159" s="1" t="str">
@@ -4354,7 +4342,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="30" x14ac:dyDescent="0.25">
@@ -4363,18 +4351,18 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/basic-commercial-conditions</v>
       </c>
       <c r="B160" s="8" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C160" s="8"/>
       <c r="D160" s="1" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F160" s="1" t="str">
         <f>A25</f>
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="161" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -4383,7 +4371,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/purchase-information</v>
       </c>
       <c r="B161" s="16" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C161" s="16"/>
       <c r="D161" s="17"/>
@@ -4400,7 +4388,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/purchase-and-reservation-information</v>
       </c>
       <c r="I161" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="162" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -4409,7 +4397,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/purchase-and-reservation-information</v>
       </c>
       <c r="B162" s="24" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C162" s="24"/>
       <c r="D162" s="22"/>
@@ -4420,7 +4408,7 @@
       </c>
       <c r="H162" s="22"/>
       <c r="I162" s="23" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="163" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -4429,7 +4417,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/defaut-transfer-times-at-interchanges</v>
       </c>
       <c r="B163" s="32" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C163" s="16"/>
       <c r="D163" s="17"/>
@@ -4446,7 +4434,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/default-transfer-times-at-interchanges</v>
       </c>
       <c r="I163" s="18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="164" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -4455,7 +4443,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/default-transfer-times-at-interchanges</v>
       </c>
       <c r="B164" s="30" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="C164" s="24"/>
       <c r="D164" s="22"/>
@@ -4466,7 +4454,7 @@
       </c>
       <c r="H164" s="22"/>
       <c r="I164" s="23" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="165" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -4475,11 +4463,11 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/existence-of-assistance-services</v>
       </c>
       <c r="B165" s="30" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C165" s="24"/>
       <c r="D165" s="22" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="E165" s="22"/>
       <c r="F165" s="22" t="str">
@@ -4488,7 +4476,7 @@
       </c>
       <c r="H165" s="22"/>
       <c r="I165" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="166" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -4497,7 +4485,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/historic-travel-and-traffic-data-and-delays</v>
       </c>
       <c r="B166" s="30" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C166" s="24"/>
       <c r="D166" s="22"/>
@@ -4508,7 +4496,7 @@
       </c>
       <c r="H166" s="22"/>
       <c r="I166" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="167" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -4517,7 +4505,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/observed-data-on-delays-and-passing-time</v>
       </c>
       <c r="B167" s="30" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C167" s="24"/>
       <c r="D167" s="22"/>
@@ -4528,7 +4516,7 @@
       </c>
       <c r="H167" s="22"/>
       <c r="I167" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="168" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -4537,7 +4525,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/observed-data-on-cancellations</v>
       </c>
       <c r="B168" s="30" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C168" s="24"/>
       <c r="D168" s="22"/>
@@ -4548,19 +4536,20 @@
       </c>
       <c r="H168" s="22"/>
       <c r="I168" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="169" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="23" t="s">
-        <v>203</v>
+      <c r="A169" s="20" t="str">
+        <f t="shared" si="5"/>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/vehicle-occupancy</v>
       </c>
       <c r="B169" s="30" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C169" s="24"/>
       <c r="D169" s="22" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="E169" s="22"/>
       <c r="F169" s="22" t="str">
@@ -4569,7 +4558,7 @@
       </c>
       <c r="H169" s="22"/>
       <c r="I169" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="170" spans="1:9" s="18" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4578,7 +4567,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-non-scheduled-transport</v>
       </c>
       <c r="B170" s="16" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C170" s="16"/>
       <c r="D170" s="17"/>
@@ -4592,10 +4581,10 @@
       </c>
       <c r="H170" s="17" t="str">
         <f>A135</f>
-        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-on-demand-services</v>
+        <v>https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-and-on-demand-services</v>
       </c>
       <c r="I170" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="171" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -4604,7 +4593,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/provider-data</v>
       </c>
       <c r="B171" s="16" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C171" s="16"/>
       <c r="D171" s="17"/>
@@ -4617,10 +4606,10 @@
         <v>1</v>
       </c>
       <c r="H171" s="18" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="I171" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="172" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -4629,7 +4618,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/public-transport-provider-data</v>
       </c>
       <c r="B172" s="24" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C172" s="24"/>
       <c r="D172" s="22"/>
@@ -4640,7 +4629,7 @@
       </c>
       <c r="H172" s="22"/>
       <c r="I172" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="173" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4649,7 +4638,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-areas-and-service-times</v>
       </c>
       <c r="B173" s="16" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C173" s="16"/>
       <c r="D173" s="17"/>
@@ -4666,7 +4655,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-area, https://w3id.org/mobilitydcat-ap/mobility-theme/hours-of-operation</v>
       </c>
       <c r="I173" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="174" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -4675,7 +4664,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-area</v>
       </c>
       <c r="B174" s="24" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C174" s="24"/>
       <c r="D174" s="22"/>
@@ -4686,7 +4675,7 @@
       </c>
       <c r="H174" s="22"/>
       <c r="I174" s="31" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="175" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -4695,7 +4684,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/locations-and-stations</v>
       </c>
       <c r="B175" s="16" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C175" s="16"/>
       <c r="D175" s="17"/>
@@ -4712,7 +4701,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/facility-location-and-features</v>
       </c>
       <c r="I175" s="18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="176" spans="1:9" s="18" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -4721,7 +4710,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/fares</v>
       </c>
       <c r="B176" s="16" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C176" s="16"/>
       <c r="D176" s="17"/>
@@ -4738,7 +4727,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/passenger-classes, https://w3id.org/mobilitydcat-ap/mobility-theme/common-fare-products, https://w3id.org/mobilitydcat-ap/mobility-theme/special-fare-products, https://w3id.org/mobilitydcat-ap/mobility-theme/basic-commercial-conditions</v>
       </c>
       <c r="I176" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="177" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -4747,7 +4736,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/reservation-and-purchase-options</v>
       </c>
       <c r="B177" s="16" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C177" s="16"/>
       <c r="D177" s="17"/>
@@ -4764,7 +4753,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/purchase-and-reservation-information</v>
       </c>
       <c r="I177" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
@@ -4773,7 +4762,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/accessibility-information-for-vehicles</v>
       </c>
       <c r="B178" s="27" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C178" s="8"/>
       <c r="F178" s="1" t="str">
@@ -4781,7 +4770,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-sub-category</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="179" spans="1:9" s="18" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4790,7 +4779,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/sharing-and-hiring-services</v>
       </c>
       <c r="B179" s="16" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C179" s="16"/>
       <c r="D179" s="17"/>
@@ -4801,7 +4790,7 @@
       </c>
       <c r="H179" s="17"/>
       <c r="I179" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="180" spans="1:9" s="23" customFormat="1" ht="198" customHeight="1" x14ac:dyDescent="0.25">
@@ -4810,7 +4799,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/sharing-hiring-and-renting-services</v>
       </c>
       <c r="B180" s="9" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C180" s="24"/>
       <c r="D180" s="22"/>
@@ -4824,7 +4813,7 @@
       </c>
       <c r="H180" s="22"/>
       <c r="I180" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="181" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -4833,7 +4822,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bike-sharing-locations-and-stations</v>
       </c>
       <c r="B181" s="16" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C181" s="16"/>
       <c r="D181" s="17"/>
@@ -4850,7 +4839,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-locations-and-stations</v>
       </c>
       <c r="I181" s="18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="182" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -4859,7 +4848,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/car-sharing-locations-and-stations</v>
       </c>
       <c r="B182" s="16" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C182" s="16"/>
       <c r="D182" s="17"/>
@@ -4876,7 +4865,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-locations-and-stations</v>
       </c>
       <c r="I182" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="183" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -4885,7 +4874,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bike-hiring-stations</v>
       </c>
       <c r="B183" s="16" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C183" s="16"/>
       <c r="D183" s="17"/>
@@ -4902,7 +4891,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-locations-and-stations</v>
       </c>
       <c r="I183" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="184" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -4911,7 +4900,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/car-hiring-stations</v>
       </c>
       <c r="B184" s="16" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C184" s="16"/>
       <c r="D184" s="17"/>
@@ -4928,7 +4917,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-locations-and-stations</v>
       </c>
       <c r="I184" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="185" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -4937,7 +4926,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/e-scooter-sharing-locations-and-stations</v>
       </c>
       <c r="B185" s="16" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C185" s="16"/>
       <c r="D185" s="17"/>
@@ -4954,7 +4943,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-locations-and-stations</v>
       </c>
       <c r="I185" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="186" spans="1:9" s="18" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4963,7 +4952,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/car-sharing-availability</v>
       </c>
       <c r="B186" s="16" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C186" s="16"/>
       <c r="D186" s="17"/>
@@ -4980,7 +4969,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-vehicle-fleet-description, https://w3id.org/mobilitydcat-ap/mobility-theme/service-real-time-availability</v>
       </c>
       <c r="I186" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="187" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -4989,7 +4978,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bike-sharing-availability</v>
       </c>
       <c r="B187" s="16" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C187" s="16"/>
       <c r="D187" s="17"/>
@@ -5006,7 +4995,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-vehicle-fleet-description, https://w3id.org/mobilitydcat-ap/mobility-theme/service-real-time-availability</v>
       </c>
       <c r="I187" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="188" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5015,7 +5004,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/car-hiring-availability</v>
       </c>
       <c r="B188" s="16" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C188" s="16"/>
       <c r="D188" s="17"/>
@@ -5032,7 +5021,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-vehicle-fleet-description, https://w3id.org/mobilitydcat-ap/mobility-theme/service-real-time-availability</v>
       </c>
       <c r="I188" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="189" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5041,7 +5030,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/bike-hiring-availability</v>
       </c>
       <c r="B189" s="16" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C189" s="16"/>
       <c r="D189" s="17"/>
@@ -5058,7 +5047,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-vehicle-fleet-description, https://w3id.org/mobilitydcat-ap/mobility-theme/service-real-time-availability</v>
       </c>
       <c r="I189" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="190" spans="1:9" s="18" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5067,7 +5056,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/e-scooter-sharing-availability</v>
       </c>
       <c r="B190" s="16" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C190" s="16"/>
       <c r="D190" s="17"/>
@@ -5084,7 +5073,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-vehicle-fleet-description, https://w3id.org/mobilitydcat-ap/mobility-theme/service-real-time-availability</v>
       </c>
       <c r="I190" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="191" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -5093,7 +5082,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-locations-and-stations</v>
       </c>
       <c r="B191" s="33" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C191" s="24"/>
       <c r="D191" s="22"/>
@@ -5104,7 +5093,7 @@
       </c>
       <c r="H191" s="22"/>
       <c r="I191" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="192" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5113,11 +5102,11 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-vehicle-fleet-description</v>
       </c>
       <c r="B192" s="24" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C192" s="24"/>
       <c r="D192" s="22" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="E192" s="22"/>
       <c r="F192" s="22" t="str">
@@ -5126,7 +5115,7 @@
       </c>
       <c r="H192" s="22"/>
       <c r="I192" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="193" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -5135,7 +5124,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-real-time-availability</v>
       </c>
       <c r="B193" s="24" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C193" s="24"/>
       <c r="D193" s="22"/>
@@ -5146,7 +5135,7 @@
       </c>
       <c r="H193" s="22"/>
       <c r="I193" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="194" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -5155,7 +5144,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-payment-methods</v>
       </c>
       <c r="B194" s="24" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C194" s="24"/>
       <c r="D194" s="22"/>
@@ -5166,7 +5155,7 @@
       </c>
       <c r="H194" s="22"/>
       <c r="I194" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="195" spans="1:9" s="23" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -5175,11 +5164,11 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-zones</v>
       </c>
       <c r="B195" s="21" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C195" s="24"/>
       <c r="D195" s="22" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="E195" s="22"/>
       <c r="F195" s="22" t="str">
@@ -5188,7 +5177,7 @@
       </c>
       <c r="H195" s="22"/>
       <c r="I195" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="196" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -5197,7 +5186,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/payment-methods</v>
       </c>
       <c r="B196" s="16" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C196" s="16"/>
       <c r="D196" s="17"/>
@@ -5214,7 +5203,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-payment-methods</v>
       </c>
       <c r="I196" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="197" spans="1:9" s="18" customFormat="1" x14ac:dyDescent="0.25">
@@ -5223,7 +5212,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/environmental-standards-for-vehicles</v>
       </c>
       <c r="B197" s="16" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C197" s="16"/>
       <c r="D197" s="17"/>
@@ -5240,7 +5229,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/service-vehicle-fleet-description</v>
       </c>
       <c r="I197" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
@@ -5249,7 +5238,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/air-and-space-travel</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C198" s="8"/>
       <c r="F198" s="1" t="str">
@@ -5257,7 +5246,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
@@ -5266,7 +5255,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/waterways-and-water-bodies</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C199" s="8"/>
       <c r="F199" s="1" t="str">
@@ -5274,7 +5263,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/data-content-category</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
@@ -5283,7 +5272,7 @@
         <v>https://w3id.org/mobilitydcat-ap/mobility-theme/other</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C200" s="8"/>
       <c r="F200" s="1" t="str">
@@ -5318,106 +5307,106 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C1" s="5"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="B2" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="C10" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="C10" s="28" t="s">
-        <v>256</v>
-      </c>
       <c r="D10" s="28" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
